--- a/stories/arbres/TREE-AUT-007.xlsx
+++ b/stories/arbres/TREE-AUT-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soleil entre. Maya ouvre les yeux. Maman dit : une étape après l'autre. D'abord se lever. Puis s'habiller. Puis déjeuner. Puis le sac. Maya écoute. Elle se lève.</t>
+          <t>Le soleil entre. Maya ouvre les yeux. Une étape après l'autre. D'abord se lever. Puis s'habiller. Puis déjeuner. Puis le sac. Maya écoute. Elle se lève.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soleil entre. Maya ouvre les yeux.
+maman|Une étape après l'autre. D'abord se lever.
+narrateur|Puis s'habiller. Puis déjeuner. Puis le sac. Maya écoute. Elle se lève.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la chambre, la salle d'eau, ou la cuisine.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers la chambre. Le lit est encore chaud. maman est tout près. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maya se prépare. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Maya a retenu. Une étape après l'autre. Maya fait l'étape dite. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2225,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2394,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le t-shirt. Une chaussette est au sol. maman montre lentement. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le sac. La couverture glisse. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le manteau. Le carrelage est frais. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3754,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi les chaussettes. Le savon sent la menthe. maman montre lentement. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3945,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4112,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le sac. Le carrelage est frais. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4279,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4446,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le manteau. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4613,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4780,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou. Un oiseau chante. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4947,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5114,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le gilet. Il y a des miettes. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5305,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5472,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le sac. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5639,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5806,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le manteau. Un oiseau chante. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5973,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5843,7 +6002,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. La lumière est claire. Maya dit : j'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
+          <t>Maya rejoint le doudou. La lumière est claire. J'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5981,6 +6140,13 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou. La lumière est claire.
+enfant-f|J'ai fini cette étape.
+narrateur|Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6309,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6476,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers la salle d'eau. L'eau coule tout doux. maman est tout près. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6483,6 +6659,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Maya se prépare. Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6507,7 +6688,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Maya respire. Une étape après l'autre. Maya fait l'étape dite. maman dit : je suis là.</t>
+          <t>Maya respire. Une étape après l'autre. Maya fait l'étape dite. Je suis là.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6649,6 +6830,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Maya respire. Une étape après l'autre. Maya fait l'étape dite.
+maman|Je suis là.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6837,6 +7024,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
         </is>
       </c>
     </row>
@@ -7001,6 +7193,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le t-shirt. La couverture glisse. maman montre lentement. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7384,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7551,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le sac. Le carrelage est frais. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7718,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7885,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le manteau. Le bol est tiède. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8052,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8219,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8386,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8553,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi les chaussettes. Le carrelage est frais. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8744,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8911,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le sac. Le bol est tiède. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9078,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9245,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le manteau. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9412,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9579,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou. La lumière est claire. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9746,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9503,7 +9775,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le gilet. Le bol est tiède. maman montre lentement. Maya dit : j'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>Maya a choisi le gilet. Le bol est tiède. maman montre lentement. J'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9641,6 +9913,13 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le gilet. Le bol est tiède. maman montre lentement.
+enfant-f|J'ai fini cette étape.
+narrateur|Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10106,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10273,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le sac. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10440,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10607,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le manteau. La lumière est claire. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10774,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10499,7 +10803,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. Le lait est blanc. Maya dit : j'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
+          <t>Maya rejoint le doudou. Le lait est blanc. J'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10637,6 +10941,13 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou. Le lait est blanc.
+enfant-f|J'ai fini cette étape.
+narrateur|Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11110,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10961,6 +11277,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers la cuisine. Ça sent le pain. maman est tout près. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11458,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Maya se prépare. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11631,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|C'est juste. Une étape après l'autre. Maya fait l'étape dite. Maya donne la main à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11493,6 +11824,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
         </is>
       </c>
     </row>
@@ -11657,6 +11993,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le t-shirt. Un oiseau chante. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12184,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12351,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le sac. Le bol est tiède. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12518,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12685,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le manteau. Un oiseau chante. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12852,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13019,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13186,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12839,7 +13215,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi les chaussettes. La lumière est claire. maman montre lentement. Maya dit : j'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>Maya a choisi les chaussettes. La lumière est claire. maman montre lentement. J'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12977,6 +13353,13 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi les chaussettes. La lumière est claire. maman montre lentement.
+enfant-f|J'ai fini cette étape.
+narrateur|Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13546,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13713,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le sac. Un oiseau chante. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13880,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14047,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le manteau. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14214,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14381,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou. Le lait est blanc. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14548,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14715,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le gilet. Le lait est blanc. maman montre lentement. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14906,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15073,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le sac. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15240,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15407,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le manteau. Le lait est blanc. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15574,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15155,7 +15603,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. Le lit est encore chaud. Maya dit : j'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
+          <t>Maya rejoint le doudou. Le lit est encore chaud. J'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15293,6 +15741,13 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou. Le lit est encore chaud.
+enfant-f|J'ai fini cette étape.
+narrateur|Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15910,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15504,6 +15964,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-007.xlsx
+++ b/stories/arbres/TREE-AUT-007.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Puis s'habiller. Puis déjeuner. Puis le sac. Maya écoute. Elle se lève.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre la chambre, la salle d'eau, ou la cuisine.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
           <t>narrateur|Maya va vers la chambre. Le lit est encore chaud. maman est tout près. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|Maya se prépare. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Oui. Maya a retenu. Une étape après l'autre. Maya fait l'étape dite. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2232,6 +2242,7 @@
           <t>narrateur|On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2399,6 +2410,7 @@
           <t>narrateur|Maya a choisi le t-shirt. Une chaussette est au sol. maman montre lentement. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,7 @@
           <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2770,7 @@
           <t>narrateur|Maya rejoint le sac. La couverture glisse. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3106,7 @@
           <t>narrateur|Maya rejoint le manteau. Le carrelage est frais. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3442,7 @@
           <t>narrateur|Maya rejoint le doudou. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3778,7 @@
           <t>narrateur|Maya a choisi les chaussettes. Le savon sent la menthe. maman montre lentement. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3950,6 +3970,7 @@
           <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4117,6 +4138,7 @@
           <t>narrateur|Maya rejoint le sac. Le carrelage est frais. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4284,6 +4306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4451,6 +4474,7 @@
           <t>narrateur|Maya rejoint le manteau. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4618,6 +4642,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4785,6 +4810,7 @@
           <t>narrateur|Maya rejoint le doudou. Un oiseau chante. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4952,6 +4978,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5119,6 +5146,7 @@
           <t>narrateur|Maya a choisi le gilet. Il y a des miettes. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5310,6 +5338,7 @@
           <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5477,6 +5506,7 @@
           <t>narrateur|Maya rejoint le sac. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5644,6 +5674,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5811,6 +5842,7 @@
           <t>narrateur|Maya rejoint le manteau. Un oiseau chante. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5978,6 +6010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6147,6 +6180,7 @@
 narrateur|Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6314,6 +6348,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6481,6 +6516,7 @@
           <t>narrateur|Maya va vers la salle d'eau. L'eau coule tout doux. maman est tout près. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6664,6 +6700,7 @@
           <t>narrateur|Maya se prépare. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6836,6 +6873,7 @@
 maman|Je suis là.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7031,6 +7069,7 @@
           <t>narrateur|On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7198,6 +7237,7 @@
           <t>narrateur|Maya a choisi le t-shirt. La couverture glisse. maman montre lentement. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7389,6 +7429,7 @@
           <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7556,6 +7597,7 @@
           <t>narrateur|Maya rejoint le sac. Le carrelage est frais. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7723,6 +7765,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7890,6 +7933,7 @@
           <t>narrateur|Maya rejoint le manteau. Le bol est tiède. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8057,6 +8101,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8224,6 +8269,7 @@
           <t>narrateur|Maya rejoint le doudou. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8391,6 +8437,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8558,6 +8605,7 @@
           <t>narrateur|Maya a choisi les chaussettes. Le carrelage est frais. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8749,6 +8797,7 @@
           <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8916,6 +8965,7 @@
           <t>narrateur|Maya rejoint le sac. Le bol est tiède. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9083,6 +9133,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9250,6 +9301,7 @@
           <t>narrateur|Maya rejoint le manteau. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9417,6 +9469,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9584,6 +9637,7 @@
           <t>narrateur|Maya rejoint le doudou. La lumière est claire. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9751,6 +9805,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9920,6 +9975,7 @@
 narrateur|Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10111,6 +10167,7 @@
           <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10278,6 +10335,7 @@
           <t>narrateur|Maya rejoint le sac. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10445,6 +10503,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10612,6 +10671,7 @@
           <t>narrateur|Maya rejoint le manteau. La lumière est claire. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10779,6 +10839,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10948,6 +11009,7 @@
 narrateur|Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11115,6 +11177,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11282,6 +11345,7 @@
           <t>narrateur|Maya va vers la cuisine. Ça sent le pain. maman est tout près. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11465,6 +11529,7 @@
           <t>narrateur|Maya se prépare. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11636,6 +11701,7 @@
           <t>narrateur|C'est juste. Une étape après l'autre. Maya fait l'étape dite. Maya donne la main à maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11831,6 +11897,7 @@
           <t>narrateur|On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11998,6 +12065,7 @@
           <t>narrateur|Maya a choisi le t-shirt. Un oiseau chante. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12189,6 +12257,7 @@
           <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12356,6 +12425,7 @@
           <t>narrateur|Maya rejoint le sac. Le bol est tiède. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12523,6 +12593,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12690,6 +12761,7 @@
           <t>narrateur|Maya rejoint le manteau. Un oiseau chante. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12857,6 +12929,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13024,6 +13097,7 @@
           <t>narrateur|Maya rejoint le doudou. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13191,6 +13265,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13360,6 +13435,7 @@
 narrateur|Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13551,6 +13627,7 @@
           <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13718,6 +13795,7 @@
           <t>narrateur|Maya rejoint le sac. Un oiseau chante. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13885,6 +13963,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14052,6 +14131,7 @@
           <t>narrateur|Maya rejoint le manteau. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14219,6 +14299,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14386,6 +14467,7 @@
           <t>narrateur|Maya rejoint le doudou. Le lait est blanc. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14553,6 +14635,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14720,6 +14803,7 @@
           <t>narrateur|Maya a choisi le gilet. Le lait est blanc. maman montre lentement. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14911,6 +14995,7 @@
           <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15078,6 +15163,7 @@
           <t>narrateur|Maya rejoint le sac. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15245,6 +15331,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15412,6 +15499,7 @@
           <t>narrateur|Maya rejoint le manteau. Le lait est blanc. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15579,6 +15667,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15748,6 +15837,7 @@
 narrateur|Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15915,6 +16005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15933,7 +16024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15971,6 +16062,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15985,7 +16090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16172,6 +16277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-007.xlsx
+++ b/stories/arbres/TREE-AUT-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maya enchaîne le matin</t>
+          <t>Le volet de Victorina</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorina se réveille dans la maison jaune. Elle veut être prête. Elle enchaîne se lever, s'habiller, déjeuner, le sac. Une étape après l'autre.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soleil entre. Maya ouvre les yeux. Une étape après l'autre. D'abord se lever. Puis s'habiller. Puis déjeuner. Puis le sac. Maya écoute. Elle se lève.</t>
+          <t>La petite maison jaune a des volets en bois. Un volet claque tout doux. Une bande de soleil glisse sur le parquet. Le parquet est tiède. Une odeur de pain monte l'escalier. Le pain est encore tout chaud. Dehors, un moineau picore la gouttière. La gouttière fait tic tic. En bas, le bol du chat tinte. Le pain est prêt. Victorina, le soleil est déjà là. La couverture de laine pique un peu. Elle sent le savon propre. Le radiateur fait un petit clic. Sur la commode, un peigne attend. En ce moment, Victorina ouvre les yeux. Maman, je me lève. D'accord. Une étape après l'autre. D'abord tu te lèves. Victorina pose les pieds sur le tapis. Le tapis est doux. Ensuite on s'habille. Puis le déjeuner. Puis le sac. Victorina écoute. Elle se lève tout doucement. Bravo. Tu as commencé. Tu as dormi, Victorina ? Oui, papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,9 +1337,37 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soleil entre. Maya ouvre les yeux.
-maman|Une étape après l'autre. D'abord se lever.
-narrateur|Puis s'habiller. Puis déjeuner. Puis le sac. Maya écoute. Elle se lève.</t>
+          <t>narrateur|La petite maison jaune a des volets en bois.
+narrateur|Un volet claque tout doux.
+narrateur|Une bande de soleil glisse sur le parquet.
+narrateur|Le parquet est tiède.
+narrateur|Une odeur de pain monte l'escalier.
+narrateur|Le pain est encore tout chaud.
+narrateur|Dehors, un moineau picore la gouttière.
+narrateur|La gouttière fait tic tic.
+narrateur|En bas, le bol du chat tinte.
+papa|Le pain est prêt.
+maman|Victorina, le soleil est déjà là.
+narrateur|La couverture de laine pique un peu.
+narrateur|Elle sent le savon propre.
+narrateur|Le radiateur fait un petit clic.
+narrateur|Sur la commode, un peigne attend.
+narrateur|En ce moment, Victorina ouvre les yeux.
+enfant-f|Maman, je me lève.
+maman|D'accord.
+maman|Une étape après l'autre.
+papa|D'abord tu te lèves.
+narrateur|Victorina pose les pieds sur le tapis.
+narrateur|Le tapis est doux.
+maman|Ensuite on s'habille.
+maman|Puis le déjeuner.
+papa|Puis le sac.
+narrateur|Victorina écoute.
+narrateur|Elle se lève tout doucement.
+maman|Bravo.
+maman|Tu as commencé.
+papa|Tu as dormi, Victorina ?
+enfant-f|Oui, papa.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1355,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la chambre, la salle d'eau, ou la cuisine.</t>
+          <t>Victorina peut aller dans la chambre, la salle d'eau, ou la cuisine.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1519,7 +1559,7 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la chambre, la salle d'eau, ou la cuisine.</t>
+          <t>narrateur|Victorina peut aller dans la chambre, la salle d'eau, ou la cuisine.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1547,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers la chambre. Le lit est encore chaud. maman est tout près. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
+          <t>Victorina pousse la porte de la chambre. Le lit est encore chaud. L'oreiller sent le savon. La couverture glisse au bord. Le lit est doux, maman. Oui. Maintenant tu te lèves. Une étape après l'autre. Victorina pose les deux pieds. Le tapis étouffe ses pas. Tu as les pieds sur le tapis ? Oui, papa. Bravo. C'est l'étape. Maman ouvre le tiroir. Les vêtements sont pliés. Ensuite on s'habille. Victorina va vers le tiroir. Elle écoute. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1687,7 +1727,26 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maya va vers la chambre. Le lit est encore chaud. maman est tout près. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
+          <t>narrateur|Victorina pousse la porte de la chambre.
+narrateur|Le lit est encore chaud.
+narrateur|L'oreiller sent le savon.
+narrateur|La couverture glisse au bord.
+enfant-f|Le lit est doux, maman.
+maman|Oui.
+maman|Maintenant tu te lèves.
+maman|Une étape après l'autre.
+narrateur|Victorina pose les deux pieds.
+narrateur|Le tapis étouffe ses pas.
+papa|Tu as les pieds sur le tapis ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|C'est l'étape.
+narrateur|Maman ouvre le tiroir.
+narrateur|Les vêtements sont pliés.
+maman|Ensuite on s'habille.
+narrateur|Victorina va vers le tiroir.
+narrateur|Elle écoute.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1715,7 +1774,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maya se prépare. Que fait-elle ?</t>
+          <t>Victorina se prépare. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1871,7 +1930,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maya se prépare. Que fait-elle ?</t>
+          <t>narrateur|Victorina se prépare.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1899,7 +1959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Maya a retenu. Une étape après l'autre. Maya fait l'étape dite. On continue avec maman.</t>
+          <t>Oui. Victorina a retenu. Une étape après l'autre. Elle s'est levée. Elle a écouté. Bravo, Victorina. Tu as fait du bon travail. On continue ? Oui, maman.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2043,7 +2103,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Maya a retenu. Une étape après l'autre. Maya fait l'étape dite. On continue avec maman.</t>
+          <t>narrateur|Oui.
+narrateur|Victorina a retenu.
+maman|Une étape après l'autre.
+narrateur|Elle s'est levée.
+narrateur|Elle a écouté.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+maman|On continue ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2071,7 +2139,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
+          <t>Ensuite, le t-shirt, les chaussettes, ou le gilet ?</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2239,7 +2307,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
+          <t>narrateur|Ensuite, le t-shirt, les chaussettes, ou le gilet ?</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2267,7 +2335,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le t-shirt. Une chaussette est au sol. maman montre lentement. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>Dans la chambre, Victorina a choisi le t-shirt. Il est plié dans le tiroir. Le coton est doux et un peu froid. Une chaussette attend encore au sol. Prends le t-shirt. C'est cette étape. Une étape après l'autre. Victorina passe la tête. Puis les manches. Les manches sont bonnes ? Oui, papa. Bravo. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2407,7 +2475,19 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le t-shirt. Une chaussette est au sol. maman montre lentement. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, Victorina a choisi le t-shirt.
+narrateur|Il est plié dans le tiroir.
+narrateur|Le coton est doux et un peu froid.
+narrateur|Une chaussette attend encore au sol.
+maman|Prends le t-shirt.
+maman|C'est cette étape.
+maman|Une étape après l'autre.
+narrateur|Victorina passe la tête.
+narrateur|Puis les manches.
+papa|Les manches sont bonnes ?
+enfant-f|Oui, papa.
+papa|Bravo.
+maman|Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2435,7 +2515,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2599,7 +2679,7 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>narrateur|Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2627,7 +2707,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le sac. La couverture glisse. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
+          <t>Victorina rejoint le sac. La fermeture du sac fait un petit tchac. Victorina ouvre le sac. Elle met la gourde. Elle ferme le sac. Le sac est prêt, maman. Tu fermes le sac. C'est cette étape. Elle a commencé dans la chambre. Elle a mis le t-shirt. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le sac tient tout seul.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2767,7 +2847,22 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le sac. La couverture glisse. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
+          <t>narrateur|Victorina rejoint le sac.
+narrateur|La fermeture du sac fait un petit tchac.
+narrateur|Victorina ouvre le sac.
+narrateur|Elle met la gourde.
+narrateur|Elle ferme le sac.
+enfant-f|Le sac est prêt, maman.
+maman|Tu fermes le sac.
+maman|C'est cette étape.
+narrateur|Elle a commencé dans la chambre.
+narrateur|Elle a mis le t-shirt.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le sac tient tout seul.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2795,7 +2890,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la chambre. Elle a mis le t-shirt. Elle a pris le sac. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le sac tient tout seul. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2935,7 +3030,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la chambre.
+narrateur|Elle a mis le t-shirt.
+narrateur|Elle a pris le sac.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le sac tient tout seul.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2963,7 +3067,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le manteau. Le carrelage est frais. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
+          <t>Victorina rejoint le manteau. Le manteau sent encore le vent d'hier. Victorina passe une manche. Puis l'autre manche. Elle ferme le bouton. Le manteau est chaud, papa. Passe les manches. Doucement. Elle a commencé dans la chambre. Elle a mis le t-shirt. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le manteau est fermé.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3103,7 +3207,22 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le manteau. Le carrelage est frais. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
+          <t>narrateur|Victorina rejoint le manteau.
+narrateur|Le manteau sent encore le vent d'hier.
+narrateur|Victorina passe une manche.
+narrateur|Puis l'autre manche.
+narrateur|Elle ferme le bouton.
+enfant-f|Le manteau est chaud, papa.
+papa|Passe les manches.
+papa|Doucement.
+narrateur|Elle a commencé dans la chambre.
+narrateur|Elle a mis le t-shirt.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le manteau est fermé.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3131,7 +3250,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la chambre. Elle a mis le t-shirt. Elle a pris le manteau. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le manteau est fermé. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3271,7 +3390,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la chambre.
+narrateur|Elle a mis le t-shirt.
+narrateur|Elle a pris le manteau.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le manteau est fermé.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3299,7 +3427,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
+          <t>Victorina rejoint le doudou. Le doudou a une oreille toute chaude. Victorina prend le doudou. Elle le serre un peu. Elle le garde contre elle. Mon doudou est là. Prends le doudou avec toi. Elle a commencé dans la chambre. Elle a mis le t-shirt. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le doudou est contre elle.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3439,7 +3567,21 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le doudou. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le t-shirt.</t>
+          <t>narrateur|Victorina rejoint le doudou.
+narrateur|Le doudou a une oreille toute chaude.
+narrateur|Victorina prend le doudou.
+narrateur|Elle le serre un peu.
+narrateur|Elle le garde contre elle.
+enfant-f|Mon doudou est là.
+maman|Prends le doudou avec toi.
+narrateur|Elle a commencé dans la chambre.
+narrateur|Elle a mis le t-shirt.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le doudou est contre elle.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3467,7 +3609,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la chambre. Elle a mis le t-shirt. Elle a pris le doudou. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le doudou est contre elle. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3607,7 +3749,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la chambre.
+narrateur|Elle a mis le t-shirt.
+narrateur|Elle a pris le doudou.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le doudou est contre elle.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3635,7 +3786,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi les chaussettes. Le savon sent la menthe. maman montre lentement. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>Dans la chambre, Victorina a choisi les chaussettes. Une chaussette est au sol. L'autre est sur la chaise. La laine est un peu rêche. D'abord le pied droit. Puis le pied gauche. Une étape après l'autre. Victorina enfile la première. Puis la deuxième. Tu as tes deux chaussettes ? Oui, papa. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3775,7 +3926,19 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi les chaussettes. Le savon sent la menthe. maman montre lentement. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, Victorina a choisi les chaussettes.
+narrateur|Une chaussette est au sol.
+narrateur|L'autre est sur la chaise.
+narrateur|La laine est un peu rêche.
+maman|D'abord le pied droit.
+maman|Puis le pied gauche.
+maman|Une étape après l'autre.
+narrateur|Victorina enfile la première.
+narrateur|Puis la deuxième.
+papa|Tu as tes deux chaussettes ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3803,7 +3966,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3967,7 +4130,7 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>narrateur|Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3995,7 +4158,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le sac. Le carrelage est frais. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
+          <t>Victorina rejoint le sac. Une miette colle au bord du sac. Victorina ouvre le sac. Elle met la gourde. Elle ferme le sac. J'ai mis la gourde. La gourde va dans le sac. Elle a commencé dans la chambre. Elle a mis les chaussettes. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. La gourde ne bouge plus.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4135,7 +4298,21 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le sac. Le carrelage est frais. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
+          <t>narrateur|Victorina rejoint le sac.
+narrateur|Une miette colle au bord du sac.
+narrateur|Victorina ouvre le sac.
+narrateur|Elle met la gourde.
+narrateur|Elle ferme le sac.
+enfant-f|J'ai mis la gourde.
+papa|La gourde va dans le sac.
+narrateur|Elle a commencé dans la chambre.
+narrateur|Elle a mis les chaussettes.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|La gourde ne bouge plus.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4163,7 +4340,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la chambre. Elle a mis les chaussettes. Elle a pris le sac. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. La gourde ne bouge plus. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4303,7 +4480,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la chambre.
+narrateur|Elle a mis les chaussettes.
+narrateur|Elle a pris le sac.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|La gourde ne bouge plus.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4331,7 +4517,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le manteau. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
+          <t>Victorina rejoint le manteau. La capuche du manteau est douce. Victorina passe une manche. Puis l'autre manche. Elle ferme le bouton. La capuche, c'est doux. La capuche, c'est après. Elle a commencé dans la chambre. Elle a mis les chaussettes. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. La capuche attend.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4471,7 +4657,21 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le manteau. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
+          <t>narrateur|Victorina rejoint le manteau.
+narrateur|La capuche du manteau est douce.
+narrateur|Victorina passe une manche.
+narrateur|Puis l'autre manche.
+narrateur|Elle ferme le bouton.
+enfant-f|La capuche, c'est doux.
+maman|La capuche, c'est après.
+narrateur|Elle a commencé dans la chambre.
+narrateur|Elle a mis les chaussettes.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|La capuche attend.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4499,7 +4699,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la chambre. Elle a mis les chaussettes. Elle a pris le manteau. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. La capuche attend. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4639,7 +4839,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la chambre.
+narrateur|Elle a mis les chaussettes.
+narrateur|Elle a pris le manteau.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|La capuche attend.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4667,7 +4876,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. Un oiseau chante. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
+          <t>Victorina rejoint le doudou. Le doudou a un petit noeud rouge. Victorina prend le doudou. Elle le serre un peu. Elle le garde contre elle. Il sent le savon. Le doudou vient avec nous. Elle a commencé dans la chambre. Elle a mis les chaussettes. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le noeud rouge est visible.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4807,7 +5016,21 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le doudou. Un oiseau chante. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis les chaussettes.</t>
+          <t>narrateur|Victorina rejoint le doudou.
+narrateur|Le doudou a un petit noeud rouge.
+narrateur|Victorina prend le doudou.
+narrateur|Elle le serre un peu.
+narrateur|Elle le garde contre elle.
+enfant-f|Il sent le savon.
+papa|Le doudou vient avec nous.
+narrateur|Elle a commencé dans la chambre.
+narrateur|Elle a mis les chaussettes.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le noeud rouge est visible.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4835,7 +5058,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la chambre. Elle a mis les chaussettes. Elle a pris le doudou. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le noeud rouge est visible. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4975,7 +5198,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la chambre.
+narrateur|Elle a mis les chaussettes.
+narrateur|Elle a pris le doudou.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le noeud rouge est visible.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5003,7 +5235,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le gilet. Il y a des miettes. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>Dans la chambre, Victorina a choisi le gilet. Le gilet est sur le dossier. La laine gratte un tout petit peu. Il y a des miettes sur le bord. On enlève les miettes. Puis tu mets le gilet. Une étape après l'autre. Victorina passe les bras. Elle cherche le premier bouton. Tu as trouvé le bouton ? Oui, papa. Bravo. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5143,7 +5375,19 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le gilet. Il y a des miettes. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, Victorina a choisi le gilet.
+narrateur|Le gilet est sur le dossier.
+narrateur|La laine gratte un tout petit peu.
+narrateur|Il y a des miettes sur le bord.
+maman|On enlève les miettes.
+maman|Puis tu mets le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina passe les bras.
+narrateur|Elle cherche le premier bouton.
+papa|Tu as trouvé le bouton ?
+enfant-f|Oui, papa.
+maman|Bravo.
+maman|Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5171,7 +5415,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5335,7 +5579,7 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>narrateur|Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5363,7 +5607,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le sac. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
+          <t>Victorina rejoint le sac. Le sac est un peu lourd. Victorina ouvre le sac. Elle met la gourde. Elle ferme le sac. Le sac est lourd. Tu portes le sac. Bravo. Elle a commencé dans la chambre. Elle a mis le gilet. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le sac pèse un peu.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5503,7 +5747,22 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le sac. Le bol est tiède. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
+          <t>narrateur|Victorina rejoint le sac.
+narrateur|Le sac est un peu lourd.
+narrateur|Victorina ouvre le sac.
+narrateur|Elle met la gourde.
+narrateur|Elle ferme le sac.
+enfant-f|Le sac est lourd.
+maman|Tu portes le sac.
+maman|Bravo.
+narrateur|Elle a commencé dans la chambre.
+narrateur|Elle a mis le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le sac pèse un peu.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5531,7 +5790,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la chambre. Elle a mis le gilet. Elle a pris le sac. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le sac pèse un peu. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5671,7 +5930,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la chambre.
+narrateur|Elle a mis le gilet.
+narrateur|Elle a pris le sac.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le sac pèse un peu.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5699,7 +5967,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le manteau. Un oiseau chante. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
+          <t>Victorina rejoint le manteau. Le manteau frotte contre le mur. Victorina passe une manche. Puis l'autre manche. Elle ferme le bouton. Le manteau frotte. Le manteau, c'est maintenant. Elle a commencé dans la chambre. Elle a mis le gilet. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le manteau ne frotte plus.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5839,7 +6107,21 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le manteau. Un oiseau chante. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
+          <t>narrateur|Victorina rejoint le manteau.
+narrateur|Le manteau frotte contre le mur.
+narrateur|Victorina passe une manche.
+narrateur|Puis l'autre manche.
+narrateur|Elle ferme le bouton.
+enfant-f|Le manteau frotte.
+papa|Le manteau, c'est maintenant.
+narrateur|Elle a commencé dans la chambre.
+narrateur|Elle a mis le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le manteau ne frotte plus.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5867,7 +6149,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la chambre. Elle a mis le gilet. Elle a pris le manteau. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le manteau ne frotte plus. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6007,7 +6289,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la chambre.
+narrateur|Elle a mis le gilet.
+narrateur|Elle a pris le manteau.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le manteau ne frotte plus.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6035,7 +6326,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. La lumière est claire. J'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
+          <t>Victorina rejoint le doudou. Le doudou sent le savon. Victorina prend le doudou. Elle le serre un peu. Elle le garde contre elle. Je le tiens. Le doudou est à toi. Elle a commencé dans la chambre. Elle a mis le gilet. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le savon sent encore.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6175,9 +6466,21 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le doudou. La lumière est claire.
-enfant-f|J'ai fini cette étape.
-narrateur|Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la chambre, puis le gilet.</t>
+          <t>narrateur|Victorina rejoint le doudou.
+narrateur|Le doudou sent le savon.
+narrateur|Victorina prend le doudou.
+narrateur|Elle le serre un peu.
+narrateur|Elle le garde contre elle.
+enfant-f|Je le tiens.
+maman|Le doudou est à toi.
+narrateur|Elle a commencé dans la chambre.
+narrateur|Elle a mis le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le savon sent encore.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6205,7 +6508,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la chambre. Elle a mis le gilet. Elle a pris le doudou. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le savon sent encore. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6345,7 +6648,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la chambre.
+narrateur|Elle a mis le gilet.
+narrateur|Elle a pris le doudou.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le savon sent encore.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6373,7 +6685,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers la salle d'eau. L'eau coule tout doux. maman est tout près. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
+          <t>Victorina entre dans la salle d'eau. Le carrelage est frais sous les pieds. L'eau coule tout doux. Le savon sent la menthe. Le miroir est un peu embué. L'eau est tiède, maman. Oui. Lave-toi le visage. C'est cette étape. Une étape après l'autre. Victorina mouille ses mains. Elle se sèche avec la serviette. La serviette est près de toi ? Oui, papa. Bravo. Ensuite on s'habille. Victorina écoute. Elle pose la serviette. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6513,7 +6825,25 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Maya va vers la salle d'eau. L'eau coule tout doux. maman est tout près. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
+          <t>narrateur|Victorina entre dans la salle d'eau.
+narrateur|Le carrelage est frais sous les pieds.
+narrateur|L'eau coule tout doux.
+narrateur|Le savon sent la menthe.
+narrateur|Le miroir est un peu embué.
+enfant-f|L'eau est tiède, maman.
+maman|Oui.
+maman|Lave-toi le visage.
+maman|C'est cette étape.
+maman|Une étape après l'autre.
+narrateur|Victorina mouille ses mains.
+narrateur|Elle se sèche avec la serviette.
+papa|La serviette est près de toi ?
+enfant-f|Oui, papa.
+papa|Bravo.
+maman|Ensuite on s'habille.
+narrateur|Victorina écoute.
+narrateur|Elle pose la serviette.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6541,7 +6871,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Maya se prépare. Que fait-elle ?</t>
+          <t>Victorina se prépare. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6697,7 +7027,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Maya se prépare. Que fait-elle ?</t>
+          <t>narrateur|Victorina se prépare.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6725,7 +7056,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Maya respire. Une étape après l'autre. Maya fait l'étape dite. Je suis là.</t>
+          <t>Victorina respire. Une étape après l'autre. Elle a lavé son visage. Elle a écouté. Je t'ai vue. Tu as fait l'étape. Bravo. On continue ensemble. D'accord.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6869,8 +7200,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Maya respire. Une étape après l'autre. Maya fait l'étape dite.
-maman|Je suis là.</t>
+          <t>narrateur|Victorina respire.
+maman|Une étape après l'autre.
+narrateur|Elle a lavé son visage.
+narrateur|Elle a écouté.
+papa|Je t'ai vue.
+papa|Tu as fait l'étape.
+maman|Bravo.
+maman|On continue ensemble.
+enfant-f|D'accord.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6898,7 +7236,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
+          <t>Ensuite, le t-shirt, les chaussettes, ou le gilet ?</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7066,7 +7404,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
+          <t>narrateur|Ensuite, le t-shirt, les chaussettes, ou le gilet ?</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7094,7 +7432,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le t-shirt. La couverture glisse. maman montre lentement. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>Après la salle d'eau, Victorina prend le t-shirt. Il est sur le crochet. Le tissu est encore un peu frais. La couverture de la chambre glisse au loin. Le visage est propre. Maintenant le t-shirt. Une étape après l'autre. Victorina passe la tête. Tu es sèche ? Oui, papa. Alors le t-shirt. Bravo. Elle tire le bas du t-shirt. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7234,7 +7572,20 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le t-shirt. La couverture glisse. maman montre lentement. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>narrateur|Après la salle d'eau, Victorina prend le t-shirt.
+narrateur|Il est sur le crochet.
+narrateur|Le tissu est encore un peu frais.
+narrateur|La couverture de la chambre glisse au loin.
+maman|Le visage est propre.
+maman|Maintenant le t-shirt.
+maman|Une étape après l'autre.
+narrateur|Victorina passe la tête.
+papa|Tu es sèche ?
+enfant-f|Oui, papa.
+papa|Alors le t-shirt.
+papa|Bravo.
+narrateur|Elle tire le bas du t-shirt.
+maman|Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7262,7 +7613,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7426,7 +7777,7 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>narrateur|Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7454,7 +7805,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le sac. Le carrelage est frais. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
+          <t>Victorina rejoint le sac. La gourde tinte dans le sac. Victorina ouvre le sac. Elle met la gourde. Elle ferme le sac. La gourde fait ting. Tu as mis la gourde ? Elle a commencé dans la salle d'eau. Elle a mis le t-shirt. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. La gourde est calme.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7594,7 +7945,21 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le sac. Le carrelage est frais. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
+          <t>narrateur|Victorina rejoint le sac.
+narrateur|La gourde tinte dans le sac.
+narrateur|Victorina ouvre le sac.
+narrateur|Elle met la gourde.
+narrateur|Elle ferme le sac.
+enfant-f|La gourde fait ting.
+papa|Tu as mis la gourde ?
+narrateur|Elle a commencé dans la salle d'eau.
+narrateur|Elle a mis le t-shirt.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|La gourde est calme.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7622,7 +7987,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la salle d'eau. Elle a mis le t-shirt. Elle a pris le sac. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. La gourde est calme. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7762,7 +8127,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la salle d'eau.
+narrateur|Elle a mis le t-shirt.
+narrateur|Elle a pris le sac.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|La gourde est calme.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7790,7 +8164,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le manteau. Le bol est tiède. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
+          <t>Victorina rejoint le manteau. Un bouton du manteau brille. Victorina passe une manche. Puis l'autre manche. Elle ferme le bouton. Le bouton brille. Tu as trouvé le bouton ? Elle a commencé dans la salle d'eau. Elle a mis le t-shirt. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le bouton est dans la boutonnière.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7930,7 +8304,21 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le manteau. Le bol est tiède. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
+          <t>narrateur|Victorina rejoint le manteau.
+narrateur|Un bouton du manteau brille.
+narrateur|Victorina passe une manche.
+narrateur|Puis l'autre manche.
+narrateur|Elle ferme le bouton.
+enfant-f|Le bouton brille.
+maman|Tu as trouvé le bouton ?
+narrateur|Elle a commencé dans la salle d'eau.
+narrateur|Elle a mis le t-shirt.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le bouton est dans la boutonnière.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7958,7 +8346,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la salle d'eau. Elle a mis le t-shirt. Elle a pris le manteau. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le bouton est dans la boutonnière. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8098,7 +8486,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la salle d'eau.
+narrateur|Elle a mis le t-shirt.
+narrateur|Elle a pris le manteau.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le bouton est dans la boutonnière.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8126,7 +8523,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
+          <t>Victorina rejoint le doudou. Le doudou a le ventre tout plat. Victorina prend le doudou. Elle le serre un peu. Elle le garde contre elle. Il est plat. Tu le tiens bien ? Elle a commencé dans la salle d'eau. Elle a mis le t-shirt. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le doudou est plat et sage.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8266,7 +8663,21 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le doudou. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le t-shirt.</t>
+          <t>narrateur|Victorina rejoint le doudou.
+narrateur|Le doudou a le ventre tout plat.
+narrateur|Victorina prend le doudou.
+narrateur|Elle le serre un peu.
+narrateur|Elle le garde contre elle.
+enfant-f|Il est plat.
+papa|Tu le tiens bien ?
+narrateur|Elle a commencé dans la salle d'eau.
+narrateur|Elle a mis le t-shirt.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le doudou est plat et sage.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8294,7 +8705,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la salle d'eau. Elle a mis le t-shirt. Elle a pris le doudou. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le doudou est plat et sage. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8434,7 +8845,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la salle d'eau.
+narrateur|Elle a mis le t-shirt.
+narrateur|Elle a pris le doudou.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le doudou est plat et sage.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8462,7 +8882,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi les chaussettes. Le carrelage est frais. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>Après la salle d'eau, Victorina prend les chaussettes. Le carrelage est encore frais. Les chaussettes sont sur le tapis. Pieds au sec d'abord. Puis les chaussettes. Une étape après l'autre. Victorina s'assoit un moment. Elle enfile la droite. Puis la gauche. Tes pieds sont au chaud ? Oui, papa. Bravo. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8602,7 +9022,19 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi les chaussettes. Le carrelage est frais. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>narrateur|Après la salle d'eau, Victorina prend les chaussettes.
+narrateur|Le carrelage est encore frais.
+narrateur|Les chaussettes sont sur le tapis.
+maman|Pieds au sec d'abord.
+maman|Puis les chaussettes.
+maman|Une étape après l'autre.
+narrateur|Victorina s'assoit un moment.
+narrateur|Elle enfile la droite.
+narrateur|Puis la gauche.
+papa|Tes pieds sont au chaud ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8630,7 +9062,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8794,7 +9226,7 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>narrateur|Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8822,7 +9254,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le sac. Le bol est tiède. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
+          <t>Victorina rejoint le sac. Le zip du sac est froid. Victorina ouvre le sac. Elle met la gourde. Elle ferme le sac. Le zip est froid. Le zip, tout doux. Elle a commencé dans la salle d'eau. Elle a mis les chaussettes. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le zip est fermé.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8962,7 +9394,21 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le sac. Le bol est tiède. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
+          <t>narrateur|Victorina rejoint le sac.
+narrateur|Le zip du sac est froid.
+narrateur|Victorina ouvre le sac.
+narrateur|Elle met la gourde.
+narrateur|Elle ferme le sac.
+enfant-f|Le zip est froid.
+maman|Le zip, tout doux.
+narrateur|Elle a commencé dans la salle d'eau.
+narrateur|Elle a mis les chaussettes.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le zip est fermé.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8990,7 +9436,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la salle d'eau. Elle a mis les chaussettes. Elle a pris le sac. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le zip est fermé. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9130,7 +9576,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la salle d'eau.
+narrateur|Elle a mis les chaussettes.
+narrateur|Elle a pris le sac.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le zip est fermé.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9158,7 +9613,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le manteau. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
+          <t>Victorina rejoint le manteau. Les manches du manteau sont longues. Victorina passe une manche. Puis l'autre manche. Elle ferme le bouton. Les manches sont longues. Les manches, une après l'autre. Elle a commencé dans la salle d'eau. Elle a mis les chaussettes. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Les manches sont en place.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9298,7 +9753,21 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le manteau. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
+          <t>narrateur|Victorina rejoint le manteau.
+narrateur|Les manches du manteau sont longues.
+narrateur|Victorina passe une manche.
+narrateur|Puis l'autre manche.
+narrateur|Elle ferme le bouton.
+enfant-f|Les manches sont longues.
+papa|Les manches, une après l'autre.
+narrateur|Elle a commencé dans la salle d'eau.
+narrateur|Elle a mis les chaussettes.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Les manches sont en place.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9326,7 +9795,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la salle d'eau. Elle a mis les chaussettes. Elle a pris le manteau. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Les manches sont en place. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9466,7 +9935,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la salle d'eau.
+narrateur|Elle a mis les chaussettes.
+narrateur|Elle a pris le manteau.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Les manches sont en place.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9494,7 +9972,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. La lumière est claire. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
+          <t>Victorina rejoint le doudou. Le doudou a un oeil brodé. Victorina prend le doudou. Elle le serre un peu. Elle le garde contre elle. Il a un oeil. Tu as regardé l'oeil ? Elle a commencé dans la salle d'eau. Elle a mis les chaussettes. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. L'oeil brodé la regarde.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9634,7 +10112,21 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le doudou. La lumière est claire. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis les chaussettes.</t>
+          <t>narrateur|Victorina rejoint le doudou.
+narrateur|Le doudou a un oeil brodé.
+narrateur|Victorina prend le doudou.
+narrateur|Elle le serre un peu.
+narrateur|Elle le garde contre elle.
+enfant-f|Il a un oeil.
+maman|Tu as regardé l'oeil ?
+narrateur|Elle a commencé dans la salle d'eau.
+narrateur|Elle a mis les chaussettes.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|L'oeil brodé la regarde.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9662,7 +10154,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la salle d'eau. Elle a mis les chaussettes. Elle a pris le doudou. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. L'oeil brodé la regarde. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9802,7 +10294,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la salle d'eau.
+narrateur|Elle a mis les chaussettes.
+narrateur|Elle a pris le doudou.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|L'oeil brodé la regarde.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9830,7 +10331,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le gilet. Le bol est tiède. maman montre lentement. J'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>Après la salle d'eau, Victorina prend le gilet. Le bol de lait attend en bas. Le gilet est chaud dans ses mains. Tu es propre. Maintenant le gilet. Une étape après l'autre. Victorina glisse les bras. Elle boutonne tout doucement. Tu as fini cette étape ? Oui, papa. J'ai fini. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9970,9 +10471,19 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le gilet. Le bol est tiède. maman montre lentement.
-enfant-f|J'ai fini cette étape.
-narrateur|Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>narrateur|Après la salle d'eau, Victorina prend le gilet.
+narrateur|Le bol de lait attend en bas.
+narrateur|Le gilet est chaud dans ses mains.
+maman|Tu es propre.
+maman|Maintenant le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina glisse les bras.
+narrateur|Elle boutonne tout doucement.
+papa|Tu as fini cette étape ?
+enfant-f|Oui, papa.
+enfant-f|J'ai fini.
+maman|Bravo.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10000,7 +10511,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10164,7 +10675,7 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>narrateur|Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10192,7 +10703,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le sac. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
+          <t>Victorina rejoint le sac. Le sac pose sur la chaise. Victorina ouvre le sac. Elle met la gourde. Elle ferme le sac. Le sac est sur la chaise. Le sac sur la chaise, d'accord. Elle a commencé dans la salle d'eau. Elle a mis le gilet. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. La chaise est vide.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10332,7 +10843,21 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le sac. Un oiseau chante. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
+          <t>narrateur|Victorina rejoint le sac.
+narrateur|Le sac pose sur la chaise.
+narrateur|Victorina ouvre le sac.
+narrateur|Elle met la gourde.
+narrateur|Elle ferme le sac.
+enfant-f|Le sac est sur la chaise.
+papa|Le sac sur la chaise, d'accord.
+narrateur|Elle a commencé dans la salle d'eau.
+narrateur|Elle a mis le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|La chaise est vide.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10360,7 +10885,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la salle d'eau. Elle a mis le gilet. Elle a pris le sac. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. La chaise est vide. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10500,7 +11025,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la salle d'eau.
+narrateur|Elle a mis le gilet.
+narrateur|Elle a pris le sac.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|La chaise est vide.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10528,7 +11062,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le manteau. La lumière est claire. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
+          <t>Victorina rejoint le manteau. Le manteau a une poche profonde. Victorina passe une manche. Puis l'autre manche. Elle ferme le bouton. La poche est grande. La poche est pour tes mains. Elle a commencé dans la salle d'eau. Elle a mis le gilet. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Les mains sont au chaud.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10668,7 +11202,21 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le manteau. La lumière est claire. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
+          <t>narrateur|Victorina rejoint le manteau.
+narrateur|Le manteau a une poche profonde.
+narrateur|Victorina passe une manche.
+narrateur|Puis l'autre manche.
+narrateur|Elle ferme le bouton.
+enfant-f|La poche est grande.
+maman|La poche est pour tes mains.
+narrateur|Elle a commencé dans la salle d'eau.
+narrateur|Elle a mis le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Les mains sont au chaud.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10696,7 +11244,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la salle d'eau. Elle a mis le gilet. Elle a pris le manteau. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Les mains sont au chaud. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10836,7 +11384,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la salle d'eau.
+narrateur|Elle a mis le gilet.
+narrateur|Elle a pris le manteau.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Les mains sont au chaud.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10864,7 +11421,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. Le lait est blanc. J'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
+          <t>Victorina rejoint le doudou. Le doudou pique un tout petit peu. Victorina prend le doudou. Elle le serre un peu. Elle le garde contre elle. Ça pique un peu. C'est la laine. C'est bien. Elle a commencé dans la salle d'eau. Elle a mis le gilet. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. La laine ne pique plus.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11004,9 +11561,22 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le doudou. Le lait est blanc.
-enfant-f|J'ai fini cette étape.
-narrateur|Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la salle d'eau, puis le gilet.</t>
+          <t>narrateur|Victorina rejoint le doudou.
+narrateur|Le doudou pique un tout petit peu.
+narrateur|Victorina prend le doudou.
+narrateur|Elle le serre un peu.
+narrateur|Elle le garde contre elle.
+enfant-f|Ça pique un peu.
+papa|C'est la laine.
+papa|C'est bien.
+narrateur|Elle a commencé dans la salle d'eau.
+narrateur|Elle a mis le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|La laine ne pique plus.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11034,7 +11604,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la salle d'eau. Elle a mis le gilet. Elle a pris le doudou. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. La laine ne pique plus. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11174,7 +11744,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la salle d'eau.
+narrateur|Elle a mis le gilet.
+narrateur|Elle a pris le doudou.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|La laine ne pique plus.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11202,7 +11781,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers la cuisine. Ça sent le pain. maman est tout près. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
+          <t>Victorina descend vers la cuisine. Ça sent le pain chaud. Le bol est déjà sur la table. Le lait est blanc et tiède. Ça sent bon, papa. Oui. Le pain est prêt. D'abord tu t'assieds. Une étape après l'autre. Victorina tire sa chaise. Elle s'assoit. Tu as les pieds par terre ? Oui, papa. Bravo. Mange un peu. Puis on s'habille. Victorina croque le pain. Elle boit une gorgée. Tu as fait du bon travail. Elle écoute la suite.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11342,7 +11921,26 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Maya va vers la cuisine. Ça sent le pain. maman est tout près. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman sourit.</t>
+          <t>narrateur|Victorina descend vers la cuisine.
+narrateur|Ça sent le pain chaud.
+narrateur|Le bol est déjà sur la table.
+narrateur|Le lait est blanc et tiède.
+enfant-f|Ça sent bon, papa.
+papa|Oui.
+papa|Le pain est prêt.
+maman|D'abord tu t'assieds.
+maman|Une étape après l'autre.
+narrateur|Victorina tire sa chaise.
+narrateur|Elle s'assoit.
+papa|Tu as les pieds par terre ?
+enfant-f|Oui, papa.
+papa|Bravo.
+maman|Mange un peu.
+maman|Puis on s'habille.
+narrateur|Victorina croque le pain.
+narrateur|Elle boit une gorgée.
+maman|Tu as fait du bon travail.
+narrateur|Elle écoute la suite.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11370,7 +11968,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Maya se prépare. Que fait-elle ?</t>
+          <t>Victorina se prépare. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11526,7 +12124,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Maya se prépare. Que fait-elle ?</t>
+          <t>narrateur|Victorina se prépare.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11554,7 +12153,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>C'est juste. Une étape après l'autre. Maya fait l'étape dite. Maya donne la main à maman.</t>
+          <t>C'est juste. Une étape après l'autre. Victorina s'est assise. Elle a mangé un peu. Bravo. Tu as fait l'étape. Tu donnes la main ? Oui, maman. Victorina donne la main.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11698,7 +12297,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|C'est juste. Une étape après l'autre. Maya fait l'étape dite. Maya donne la main à maman.</t>
+          <t>narrateur|C'est juste.
+maman|Une étape après l'autre.
+narrateur|Victorina s'est assise.
+narrateur|Elle a mangé un peu.
+papa|Bravo.
+papa|Tu as fait l'étape.
+maman|Tu donnes la main ?
+enfant-f|Oui, maman.
+narrateur|Victorina donne la main.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11726,7 +12333,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
+          <t>Ensuite, le t-shirt, les chaussettes, ou le gilet ?</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11894,7 +12501,7 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le t-shirt, les chaussettes, ou le gilet.</t>
+          <t>narrateur|Ensuite, le t-shirt, les chaussettes, ou le gilet ?</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11922,7 +12529,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le t-shirt. Un oiseau chante. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>Après le pain, Victorina prend le t-shirt. Un oiseau chante près de la fenêtre. Le t-shirt est sur la chaise de la cuisine. Le déjeuner est commencé. Maintenant le t-shirt. Une étape après l'autre. Victorina essuie une miette. Elle met le t-shirt. Tu ranges la miette ? Oui, papa. Bravo. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12062,7 +12669,18 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le t-shirt. Un oiseau chante. maman montre lentement. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>narrateur|Après le pain, Victorina prend le t-shirt.
+narrateur|Un oiseau chante près de la fenêtre.
+narrateur|Le t-shirt est sur la chaise de la cuisine.
+maman|Le déjeuner est commencé.
+maman|Maintenant le t-shirt.
+maman|Une étape après l'autre.
+narrateur|Victorina essuie une miette.
+narrateur|Elle met le t-shirt.
+papa|Tu ranges la miette ?
+enfant-f|Oui, papa.
+papa|Bravo.
+maman|Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12090,7 +12708,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12254,7 +12872,7 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>narrateur|Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12282,7 +12900,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le sac. Le bol est tiède. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
+          <t>Victorina rejoint le sac. Une ficelle pend du sac. Victorina ouvre le sac. Elle met la gourde. Elle ferme le sac. Il y a une ficelle. La ficelle, on la range. Elle a commencé dans la cuisine. Elle a mis le t-shirt. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. La ficelle est rentrée.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12422,7 +13040,21 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le sac. Le bol est tiède. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
+          <t>narrateur|Victorina rejoint le sac.
+narrateur|Une ficelle pend du sac.
+narrateur|Victorina ouvre le sac.
+narrateur|Elle met la gourde.
+narrateur|Elle ferme le sac.
+enfant-f|Il y a une ficelle.
+maman|La ficelle, on la range.
+narrateur|Elle a commencé dans la cuisine.
+narrateur|Elle a mis le t-shirt.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|La ficelle est rentrée.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12450,7 +13082,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la cuisine. Elle a mis le t-shirt. Elle a pris le sac. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. La ficelle est rentrée. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12590,7 +13222,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la cuisine.
+narrateur|Elle a mis le t-shirt.
+narrateur|Elle a pris le sac.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|La ficelle est rentrée.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12618,7 +13259,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le manteau. Un oiseau chante. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
+          <t>Victorina rejoint le manteau. Le col du manteau est chaud. Victorina passe une manche. Puis l'autre manche. Elle ferme le bouton. Le col est chaud. Le col te tient chaud. Elle a commencé dans la cuisine. Elle a mis le t-shirt. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le col est relevé.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12758,7 +13399,21 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le manteau. Un oiseau chante. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
+          <t>narrateur|Victorina rejoint le manteau.
+narrateur|Le col du manteau est chaud.
+narrateur|Victorina passe une manche.
+narrateur|Puis l'autre manche.
+narrateur|Elle ferme le bouton.
+enfant-f|Le col est chaud.
+papa|Le col te tient chaud.
+narrateur|Elle a commencé dans la cuisine.
+narrateur|Elle a mis le t-shirt.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le col est relevé.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12786,7 +13441,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la cuisine. Elle a mis le t-shirt. Elle a pris le manteau. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le col est relevé. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12926,7 +13581,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la cuisine.
+narrateur|Elle a mis le t-shirt.
+narrateur|Elle a pris le manteau.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le col est relevé.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12954,7 +13618,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
+          <t>Victorina rejoint le doudou. Le doudou a une tache de lait. Victorina prend le doudou. Elle le serre un peu. Elle le garde contre elle. Il a du lait. On essuie le lait plus tard. Elle a commencé dans la cuisine. Elle a mis le t-shirt. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. La tache peut attendre.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13094,7 +13758,21 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le doudou. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le t-shirt.</t>
+          <t>narrateur|Victorina rejoint le doudou.
+narrateur|Le doudou a une tache de lait.
+narrateur|Victorina prend le doudou.
+narrateur|Elle le serre un peu.
+narrateur|Elle le garde contre elle.
+enfant-f|Il a du lait.
+maman|On essuie le lait plus tard.
+narrateur|Elle a commencé dans la cuisine.
+narrateur|Elle a mis le t-shirt.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|La tache peut attendre.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13122,7 +13800,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la cuisine. Elle a mis le t-shirt. Elle a pris le doudou. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. La tache peut attendre. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13262,7 +13940,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la cuisine.
+narrateur|Elle a mis le t-shirt.
+narrateur|Elle a pris le doudou.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|La tache peut attendre.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13290,7 +13977,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi les chaussettes. La lumière est claire. maman montre lentement. J'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>Après le pain, Victorina prend les chaussettes. Le carrelage de la cuisine est lisse. Les chaussettes sont près de la chaise. Tu as mangé un peu. Maintenant les chaussettes. Une étape après l'autre. Victorina enfile la première. Puis l'autre. Tes pieds ne glissent plus ? Non, papa. Bravo. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13430,9 +14117,18 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi les chaussettes. La lumière est claire. maman montre lentement.
-enfant-f|J'ai fini cette étape.
-narrateur|Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>narrateur|Après le pain, Victorina prend les chaussettes.
+narrateur|Le carrelage de la cuisine est lisse.
+narrateur|Les chaussettes sont près de la chaise.
+maman|Tu as mangé un peu.
+maman|Maintenant les chaussettes.
+maman|Une étape après l'autre.
+narrateur|Victorina enfile la première.
+narrateur|Puis l'autre.
+papa|Tes pieds ne glissent plus ?
+enfant-f|Non, papa.
+maman|Bravo.
+maman|Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13460,7 +14156,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13624,7 +14320,7 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>narrateur|Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13652,7 +14348,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le sac. Un oiseau chante. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
+          <t>Victorina rejoint le sac. Le sac touche le sol tout doux. Victorina ouvre le sac. Elle met la gourde. Elle ferme le sac. Le sac touche le sol. Le sac reste près de toi. Elle a commencé dans la cuisine. Elle a mis les chaussettes. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le sac ne touche plus le sol.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13792,7 +14488,21 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le sac. Un oiseau chante. Maya écoute maman. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
+          <t>narrateur|Victorina rejoint le sac.
+narrateur|Le sac touche le sol tout doux.
+narrateur|Victorina ouvre le sac.
+narrateur|Elle met la gourde.
+narrateur|Elle ferme le sac.
+enfant-f|Le sac touche le sol.
+papa|Le sac reste près de toi.
+narrateur|Elle a commencé dans la cuisine.
+narrateur|Elle a mis les chaussettes.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le sac ne touche plus le sol.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13820,7 +14530,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la cuisine. Elle a mis les chaussettes. Elle a pris le sac. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le sac ne touche plus le sol. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13960,7 +14670,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la cuisine.
+narrateur|Elle a mis les chaussettes.
+narrateur|Elle a pris le sac.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le sac ne touche plus le sol.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13988,7 +14707,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le manteau. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
+          <t>Victorina rejoint le manteau. Le manteau glisse du crochet. Victorina passe une manche. Puis l'autre manche. Elle ferme le bouton. Il glisse, papa. Attrape le manteau. Doucement. Elle a commencé dans la cuisine. Elle a mis les chaussettes. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le crochet est vide.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14128,7 +14847,22 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le manteau. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
+          <t>narrateur|Victorina rejoint le manteau.
+narrateur|Le manteau glisse du crochet.
+narrateur|Victorina passe une manche.
+narrateur|Puis l'autre manche.
+narrateur|Elle ferme le bouton.
+enfant-f|Il glisse, papa.
+maman|Attrape le manteau.
+maman|Doucement.
+narrateur|Elle a commencé dans la cuisine.
+narrateur|Elle a mis les chaussettes.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le crochet est vide.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14156,7 +14890,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la cuisine. Elle a mis les chaussettes. Elle a pris le manteau. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le crochet est vide. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14296,7 +15030,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la cuisine.
+narrateur|Elle a mis les chaussettes.
+narrateur|Elle a pris le manteau.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le crochet est vide.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14324,7 +15067,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. Le lait est blanc. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
+          <t>Victorina rejoint le doudou. Le doudou tombe dans les bras. Victorina prend le doudou. Elle le serre un peu. Elle le garde contre elle. Je l'ai, maman. Le doudou dans tes bras. Elle a commencé dans la cuisine. Elle a mis les chaussettes. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Les bras sont pleins.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14464,7 +15207,21 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le doudou. Le lait est blanc. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis les chaussettes.</t>
+          <t>narrateur|Victorina rejoint le doudou.
+narrateur|Le doudou tombe dans les bras.
+narrateur|Victorina prend le doudou.
+narrateur|Elle le serre un peu.
+narrateur|Elle le garde contre elle.
+enfant-f|Je l'ai, maman.
+papa|Le doudou dans tes bras.
+narrateur|Elle a commencé dans la cuisine.
+narrateur|Elle a mis les chaussettes.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Les bras sont pleins.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14492,7 +15249,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la cuisine. Elle a mis les chaussettes. Elle a pris le doudou. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Les bras sont pleins. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14632,7 +15389,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la cuisine.
+narrateur|Elle a mis les chaussettes.
+narrateur|Elle a pris le doudou.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Les bras sont pleins.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14660,7 +15426,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le gilet. Le lait est blanc. maman montre lentement. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>Après le pain, Victorina prend le gilet. Le lait est encore blanc dans le bol. Le gilet pend au dossier. Le ventre est un peu plein. Maintenant le gilet. Une étape après l'autre. Victorina passe les bras. Elle dit tout bas. J'ai fini cette étape. Oui. Bravo. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14800,7 +15566,18 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Maya a choisi le gilet. Le lait est blanc. maman montre lentement. Maya fait l'étape dite. Une étape après l'autre. Maya fait l'étape dite. papa n'est pas loin.</t>
+          <t>narrateur|Après le pain, Victorina prend le gilet.
+narrateur|Le lait est encore blanc dans le bol.
+narrateur|Le gilet pend au dossier.
+maman|Le ventre est un peu plein.
+maman|Maintenant le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina passe les bras.
+narrateur|Elle dit tout bas.
+enfant-f|J'ai fini cette étape.
+papa|Oui.
+papa|Bravo.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14828,7 +15605,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14992,7 +15769,7 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le sac, le manteau, ou le doudou.</t>
+          <t>narrateur|Ensuite, le sac, le manteau, ou le doudou ?</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15020,7 +15797,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le sac. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
+          <t>Victorina rejoint le sac. Le sac a une poche pour la gourde. Victorina ouvre le sac. Elle met la gourde. Elle ferme le sac. La gourde est dedans. La poche de la gourde, oui. Elle a commencé dans la cuisine. Elle a mis le gilet. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. La gourde est bien.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15160,7 +15937,21 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le sac. La lumière est claire. Maya passe à l'étape suivante. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
+          <t>narrateur|Victorina rejoint le sac.
+narrateur|Le sac a une poche pour la gourde.
+narrateur|Victorina ouvre le sac.
+narrateur|Elle met la gourde.
+narrateur|Elle ferme le sac.
+enfant-f|La gourde est dedans.
+maman|La poche de la gourde, oui.
+narrateur|Elle a commencé dans la cuisine.
+narrateur|Elle a mis le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|La gourde est bien.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15188,7 +15979,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la cuisine. Elle a mis le gilet. Elle a pris le sac. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. La gourde est bien. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15328,7 +16119,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la cuisine.
+narrateur|Elle a mis le gilet.
+narrateur|Elle a pris le sac.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|La gourde est bien.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15356,7 +16156,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le manteau. Le lait est blanc. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
+          <t>Victorina rejoint le manteau. Le manteau sent le dehors. Victorina passe une manche. Puis l'autre manche. Elle ferme le bouton. Ça sent dehors. On va dehors après. Elle a commencé dans la cuisine. Elle a mis le gilet. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. L'air du dehors attend.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15496,7 +16296,21 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le manteau. Le lait est blanc. Maya range un objet. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
+          <t>narrateur|Victorina rejoint le manteau.
+narrateur|Le manteau sent le dehors.
+narrateur|Victorina passe une manche.
+narrateur|Puis l'autre manche.
+narrateur|Elle ferme le bouton.
+enfant-f|Ça sent dehors.
+papa|On va dehors après.
+narrateur|Elle a commencé dans la cuisine.
+narrateur|Elle a mis le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|L'air du dehors attend.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15524,7 +16338,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la cuisine. Elle a mis le gilet. Elle a pris le manteau. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. L'air du dehors attend. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15664,7 +16478,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la cuisine.
+narrateur|Elle a mis le gilet.
+narrateur|Elle a pris le manteau.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|L'air du dehors attend.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15692,7 +16515,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou. Le lit est encore chaud. J'ai fini cette étape. Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
+          <t>Victorina rejoint le doudou. Le doudou est prêt contre elle. Victorina prend le doudou. Elle le serre un peu. Elle le garde contre elle. Il est contre moi. Il reste avec toi. Elle a commencé dans la cuisine. Elle a mis le gilet. Une étape après l'autre. Victorina fait cette étape. Bravo. Tu as fait du bon travail. Merci. Le doudou ne tombe plus.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15832,9 +16655,21 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Maya rejoint le doudou. Le lit est encore chaud.
-enfant-f|J'ai fini cette étape.
-narrateur|Une étape après l'autre. Maya fait l'étape dite. maman dit merci. la cuisine, puis le gilet.</t>
+          <t>narrateur|Victorina rejoint le doudou.
+narrateur|Le doudou est prêt contre elle.
+narrateur|Victorina prend le doudou.
+narrateur|Elle le serre un peu.
+narrateur|Elle le garde contre elle.
+enfant-f|Il est contre moi.
+maman|Il reste avec toi.
+narrateur|Elle a commencé dans la cuisine.
+narrateur|Elle a mis le gilet.
+maman|Une étape après l'autre.
+narrateur|Victorina fait cette étape.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+enfant-f|Merci.
+narrateur|Le doudou ne tombe plus.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15862,7 +16697,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorina a commencé dans la cuisine. Elle a mis le gilet. Elle a pris le doudou. Une étape après l'autre. Bravo, Victorina. Tu as fait du bon travail. Je suis prête. Le doudou ne tombe plus. Le pain sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16002,7 +16837,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Victorina a commencé dans la cuisine.
+narrateur|Elle a mis le gilet.
+narrateur|Elle a pris le doudou.
+maman|Une étape après l'autre.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+enfant-f|Je suis prête.
+narrateur|Le doudou ne tombe plus.
+narrateur|Le pain sent encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16024,7 +16868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16076,6 +16920,13 @@
       <c r="A7" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-007.xlsx
+++ b/stories/arbres/TREE-AUT-007.xlsx
@@ -2339,17 +2339,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le t-shirt, le coton froid. Je le mets, et je tire ! Elle enfile trop vite, une manche se coince. Son épaule reste coincée, comme le volet. Sors le bras, sans tirer le bois. Le coton d'abord, ensuite la poignée. La manche me tient ! Elle ralentit, et le bras passe, tout net. Le t-shirt sent le soleil, contre sa peau. Tu peux pousser, avec l'épaule. J'ai le coton, et après ?</t>
+          <t>Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le t-shirt, le coton froid. Je le mets, et je tire ! Elle enfile trop vite, une manche se coince. Son épaule reste coincée, comme le volet. Sors le bras, sans tirer le bois. Le coton te tient le bras, attends. La manche me tient ! Elle ralentit, et le bras passe, tout net. Le t-shirt sent le soleil, contre sa peau. Tu peux pousser, avec l'épaule. J'ai le coton, et après ?</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le &lt;emphasis level="moderate"&gt;t-shirt&lt;/emphasis&gt;, le coton froid. Je le mets, et je tire ! Elle enfile trop vite, une manche se coince. Son épaule reste coincée, comme le volet. Sors le bras, sans tirer le bois. Le coton d'abord, ensuite la poignée. La manche me tient ! Elle ralentit, et le bras passe, tout net. Le t-shirt sent le soleil, contre sa peau. Tu peux pousser, avec l'épaule. J'ai le coton, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le &lt;emphasis level="moderate"&gt;t-shirt&lt;/emphasis&gt;, le coton froid. Je le mets, et je tire ! Elle enfile trop vite, une manche se coince. Son épaule reste coincée, comme le volet. Sors le bras, sans tirer le bois. Le coton te tient le bras, attends. La manche me tient ! Elle ralentit, et le bras passe, tout net. Le t-shirt sent le soleil, contre sa peau. Tu peux pousser, avec l'épaule. J'ai le coton, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le &lt;emphasis&gt;t-shirt&lt;/emphasis&gt;, le coton froid. Je le mets, et je tire ! Elle enfile trop vite, une manche se coince. Son épaule reste coincée, comme le volet. Sors le bras, sans tirer le bois. Le coton d'abord, ensuite la poignée. La manche me tient ! Elle ralentit, et le bras passe, tout net. Le t-shirt sent le soleil, contre sa peau. Tu peux pousser, avec l'épaule. J'ai le coton, et après ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le &lt;emphasis&gt;t-shirt&lt;/emphasis&gt;, le coton froid. Je le mets, et je tire ! Elle enfile trop vite, une manche se coince. Son épaule reste coincée, comme le volet. Sors le bras, sans tirer le bois. Le coton te tient le bras, attends. La manche me tient ! Elle ralentit, et le bras passe, tout net. Le t-shirt sent le soleil, contre sa peau. Tu peux pousser, avec l'épaule. J'ai le coton, et après ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -2493,7 +2493,7 @@
 narrateur|Elle enfile trop vite, une manche se coince.
 narrateur|Son épaule reste coincée, comme le volet.
 papa|Sors le bras, sans tirer le bois.
-maman|Le coton d'abord, ensuite la poignée.
+maman|Le coton te tient le bras, attends.
 enfant-f|La manche me tient !
 narrateur|Elle ralentit, et le bras passe, tout net.
 narrateur|Le t-shirt sent le soleil, contre sa peau.
@@ -2912,17 +2912,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le sac, et le volet a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. L'oiseau de papier dort dans le sac, face à la rue.</t>
+          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le sac, et le volet a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Le sac a pris le soleil, toi. L'oiseau de papier dort dans le sac, face à la rue.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le sac, et le &lt;emphasis level="moderate"&gt;volet&lt;/emphasis&gt; a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. L'oiseau de papier dort dans le sac, face à la rue.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le sac, et le &lt;emphasis level="moderate"&gt;volet&lt;/emphasis&gt; a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Le sac a pris le soleil, toi. L'oiseau de papier dort dans le sac, face à la rue.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le sac, et le &lt;emphasis&gt;volet&lt;/emphasis&gt; a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. L'oiseau de papier dort dans le sac, face à la rue.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le sac, et le &lt;emphasis&gt;volet&lt;/emphasis&gt; a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Le sac a pris le soleil, toi. L'oiseau de papier dort dans le sac, face à la rue.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -3065,7 +3065,7 @@
 enfant-f|J'ai mis le t-shirt, le sac, et le volet a ouvert.
 narrateur|Sur la chaise de la chambre, le linge s'est tu.
 narrateur|À table, le pain casse, tiède, sous les doigts.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le sac a pris le soleil, toi.
 narrateur|L'oiseau de papier dort dans le sac, face à la rue.</t>
         </is>
       </c>
@@ -3283,17 +3283,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le manteau, et le vent est entré. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Un carré de soleil tient sur le manteau, près du bois ouvert.</t>
+          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le manteau, et le vent est entré. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Le vent est entré dans tes manches. Un carré de soleil tient sur le manteau, près du bois ouvert.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le manteau, et le vent est entré. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Un carré de soleil tient sur le manteau, près du bois ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le manteau, et le vent est entré. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Le vent est entré dans tes manches. Un carré de soleil tient sur le manteau, près du bois ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le manteau, et le vent est entré. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Un carré de soleil tient sur le manteau, près du bois ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le manteau, et le vent est entré. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Le vent est entré dans tes manches. Un carré de soleil tient sur le manteau, près du bois ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -3432,7 +3432,7 @@
 enfant-f|J'ai mis le t-shirt, le manteau, et le vent est entré.
 narrateur|Sur la chaise de la chambre, le linge s'est tu.
 narrateur|À table, une goutte de lait fait un rond.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le vent est entré dans tes manches.
 narrateur|Un carré de soleil tient sur le manteau, près du bois ouvert.</t>
         </is>
       </c>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le doudou a vu la rue. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou regarde la rue, le menton sur la latte.</t>
+          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le doudou a vu la rue. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Le doudou a gardé la latte. Le doudou regarde la rue, le menton sur la latte.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le doudou a vu la rue. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou regarde la rue, le menton sur la latte.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le doudou a vu la rue. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Le doudou a gardé la latte. Le doudou regarde la rue, le menton sur la latte.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le doudou a vu la rue. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou regarde la rue, le menton sur la latte.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le t-shirt, le doudou a vu la rue. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Le doudou a gardé la latte. Le doudou regarde la rue, le menton sur la latte.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -3799,7 +3799,7 @@
 enfant-f|J'ai mis le t-shirt, le doudou a vu la rue.
 narrateur|Sur la chaise de la chambre, le linge s'est tu.
 narrateur|À table, le moineau chante, trop loin pour le bol.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le doudou a gardé la latte.
 narrateur|Le doudou regarde la rue, le menton sur la latte.</t>
         </is>
       </c>
@@ -3832,17 +3832,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Dans la chambre, le volet reste coincé, trop lourd. Victorina prend les chaussettes, un peu froides. Je les mets, et je grimpe ! Elle enfile une seule, et court au tabouret. Le pied nu glisse sur le parquet, trop lisse. Les deux pieds, sinon le tabouret part. Une chaussette, puis l'autre, sans sauter. J'ai failli tomber ! Elle s'assoit, et la deuxième chaussette passe. Le parquet n'attrape plus ses talons. Tu peux grimper, sans glisser. J'ai les deux, et après ?</t>
+          <t>Dans la chambre, le volet reste coincé, trop lourd. Victorina prend les chaussettes, un peu froides. Je les mets, et je grimpe ! Elle enfile une seule, et court au tabouret. Le pied nu glisse sur le parquet, trop lisse. Les deux pieds, sinon le tabouret part. Assieds-toi, le parquet est trop lisse. J'ai failli tomber ! Elle s'assoit, et la deuxième chaussette passe. Le parquet n'attrape plus ses talons. Tu peux grimper, sans glisser. J'ai les deux, et après ?</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend les &lt;emphasis level="moderate"&gt;chaussettes&lt;/emphasis&gt;, un peu froides. Je les mets, et je grimpe ! Elle enfile une seule, et court au tabouret. Le pied nu glisse sur le parquet, trop lisse. Les deux pieds, sinon le tabouret part. Une chaussette, puis l'autre, sans sauter. J'ai failli tomber ! Elle s'assoit, et la deuxième chaussette passe. Le parquet n'attrape plus ses talons. Tu peux grimper, sans glisser. J'ai les deux, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend les &lt;emphasis level="moderate"&gt;chaussettes&lt;/emphasis&gt;, un peu froides. Je les mets, et je grimpe ! Elle enfile une seule, et court au tabouret. Le pied nu glisse sur le parquet, trop lisse. Les deux pieds, sinon le tabouret part. Assieds-toi, le parquet est trop lisse. J'ai failli tomber ! Elle s'assoit, et la deuxième chaussette passe. Le parquet n'attrape plus ses talons. Tu peux grimper, sans glisser. J'ai les deux, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend les &lt;emphasis&gt;chaussettes&lt;/emphasis&gt;, un peu froides. Je les mets, et je grimpe ! Elle enfile une seule, et court au tabouret. Le pied nu glisse sur le parquet, trop lisse. Les deux pieds, sinon le tabouret part. Une chaussette, puis l'autre, sans sauter. J'ai failli tomber ! Elle s'assoit, et la deuxième chaussette passe. Le parquet n'attrape plus ses talons. Tu peux grimper, sans glisser. J'ai les deux, et après ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend les &lt;emphasis&gt;chaussettes&lt;/emphasis&gt;, un peu froides. Je les mets, et je grimpe ! Elle enfile une seule, et court au tabouret. Le pied nu glisse sur le parquet, trop lisse. Les deux pieds, sinon le tabouret part. Assieds-toi, le parquet est trop lisse. J'ai failli tomber ! Elle s'assoit, et la deuxième chaussette passe. Le parquet n'attrape plus ses talons. Tu peux grimper, sans glisser. J'ai les deux, et après ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -3986,7 +3986,7 @@
 narrateur|Elle enfile une seule, et court au tabouret.
 narrateur|Le pied nu glisse sur le parquet, trop lisse.
 papa|Les deux pieds, sinon le tabouret part.
-maman|Une chaussette, puis l'autre, sans sauter.
+maman|Assieds-toi, le parquet est trop lisse.
 enfant-f|J'ai failli tomber !
 narrateur|Elle s'assoit, et la deuxième chaussette passe.
 narrateur|Le parquet n'attrape plus ses talons.
@@ -4404,17 +4404,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le sac, et j'ai grimpé. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Une chaussette garde un peu de parquet, sous le sac ouvert.</t>
+          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le sac, et j'ai grimpé. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tes pieds n'ont pas glissé, sur le bois. Une chaussette garde un peu de parquet, sous le sac ouvert.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le sac, et j'ai grimpé. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Une chaussette garde un peu de parquet, sous le sac ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le sac, et j'ai grimpé. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tes pieds n'ont pas glissé, sur le bois. Une chaussette garde un peu de parquet, sous le sac ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le sac, et j'ai grimpé. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Une chaussette garde un peu de parquet, sous le sac ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le sac, et j'ai grimpé. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tes pieds n'ont pas glissé, sur le bois. Une chaussette garde un peu de parquet, sous le sac ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -4553,7 +4553,7 @@
 enfant-f|J'ai mis les chaussettes, le sac, et j'ai grimpé.
 narrateur|Sur la chaise de la chambre, le linge s'est tu.
 narrateur|À table, le pain casse, tiède, sous les doigts.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Tes pieds n'ont pas glissé, sur le bois.
 narrateur|Une chaussette garde un peu de parquet, sous le sac ouvert.</t>
         </is>
       </c>
@@ -4770,17 +4770,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le manteau, sans glisser. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau, près des chaussettes, sent le pain et le vent.</t>
+          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le manteau, sans glisser. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu pourras descendre, le manteau est prêt. Le manteau, près des chaussettes, sent le pain et le vent.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le manteau, sans glisser. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau, près des chaussettes, sent le pain et le vent.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le manteau, sans glisser. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu pourras descendre, le manteau est prêt. Le manteau, près des chaussettes, sent le pain et le vent.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le manteau, sans glisser. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau, près des chaussettes, sent le pain et le vent.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le manteau, sans glisser. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu pourras descendre, le manteau est prêt. Le manteau, près des chaussettes, sent le pain et le vent.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -4919,7 +4919,7 @@
 enfant-f|J'ai mis les chaussettes, le manteau, sans glisser.
 narrateur|Sur la chaise de la chambre, le linge s'est tu.
 narrateur|À table, une goutte de lait fait un rond.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Tu pourras descendre, le manteau est prêt.
 narrateur|Le manteau, près des chaussettes, sent le pain et le vent.</t>
         </is>
       </c>
@@ -5136,17 +5136,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le doudou sur le tabouret. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, assis sur une chaussette, voit le moineau.</t>
+          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le doudou sur le tabouret. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Le tabouret est resté droit, lui. Le doudou, assis sur une chaussette, voit le moineau.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le doudou sur le tabouret. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, assis sur une chaussette, voit le moineau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le doudou sur le tabouret. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Le tabouret est resté droit, lui. Le doudou, assis sur une chaussette, voit le moineau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le doudou sur le tabouret. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, assis sur une chaussette, voit le moineau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis les chaussettes, le doudou sur le tabouret. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Le tabouret est resté droit, lui. Le doudou, assis sur une chaussette, voit le moineau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -5285,7 +5285,7 @@
 enfant-f|J'ai mis les chaussettes, le doudou sur le tabouret.
 narrateur|Sur la chaise de la chambre, le linge s'est tu.
 narrateur|À table, le moineau chante, trop loin pour le bol.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le tabouret est resté droit, lui.
 narrateur|Le doudou, assis sur une chaussette, voit le moineau.</t>
         </is>
       </c>
@@ -5318,17 +5318,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le gilet, la laine un peu rêche. Je le mets, et je pousse ! Elle enfile trop vite, un bouton saute. La poignée froide lui pique la paume, trop nue. Le bouton d'abord, ensuite le bois. La laine tiédit tes épaules, et tes mains. Le bouton m'a échappé ! Elle le retrouve, sous la chaise, sans courir. Le gilet ferme, et la poche attend, vide. Tu peux pousser, l'épaule au chaud. J'ai la laine, et après ?</t>
+          <t>Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le gilet, la laine un peu rêche. Je le mets, et je pousse ! Elle enfile trop vite, un bouton saute. La poignée froide lui pique la paume, trop nue. Le bouton a sauté, le bois peut attendre. La laine tiédit tes épaules, et tes mains. Le bouton m'a échappé ! Elle le retrouve, sous la chaise, sans courir. Le gilet ferme, et la poche attend, vide. Tu peux pousser, l'épaule au chaud. J'ai la laine, et après ?</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le &lt;emphasis level="moderate"&gt;gilet&lt;/emphasis&gt;, la laine un peu rêche. Je le mets, et je pousse ! Elle enfile trop vite, un bouton saute. La poignée froide lui pique la paume, trop nue. Le bouton d'abord, ensuite le bois. La laine tiédit tes épaules, et tes mains. Le bouton m'a échappé ! Elle le retrouve, sous la chaise, sans courir. Le gilet ferme, et la poche attend, vide. Tu peux pousser, l'épaule au chaud. J'ai la laine, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le &lt;emphasis level="moderate"&gt;gilet&lt;/emphasis&gt;, la laine un peu rêche. Je le mets, et je pousse ! Elle enfile trop vite, un bouton saute. La poignée froide lui pique la paume, trop nue. Le bouton a sauté, le bois peut attendre. La laine tiédit tes épaules, et tes mains. Le bouton m'a échappé ! Elle le retrouve, sous la chaise, sans courir. Le gilet ferme, et la poche attend, vide. Tu peux pousser, l'épaule au chaud. J'ai la laine, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le &lt;emphasis&gt;gilet&lt;/emphasis&gt;, la laine un peu rêche. Je le mets, et je pousse ! Elle enfile trop vite, un bouton saute. La poignée froide lui pique la paume, trop nue. Le bouton d'abord, ensuite le bois. La laine tiédit tes épaules, et tes mains. Le bouton m'a échappé ! Elle le retrouve, sous la chaise, sans courir. Le gilet ferme, et la poche attend, vide. Tu peux pousser, l'épaule au chaud. J'ai la laine, et après ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Dans la chambre, le volet reste coincé, trop lourd. Victorina prend le &lt;emphasis&gt;gilet&lt;/emphasis&gt;, la laine un peu rêche. Je le mets, et je pousse ! Elle enfile trop vite, un bouton saute. La poignée froide lui pique la paume, trop nue. Le bouton a sauté, le bois peut attendre. La laine tiédit tes épaules, et tes mains. Le bouton m'a échappé ! Elle le retrouve, sous la chaise, sans courir. Le gilet ferme, et la poche attend, vide. Tu peux pousser, l'épaule au chaud. J'ai la laine, et après ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -5471,7 +5471,7 @@
 enfant-f|Je le mets, et je pousse !
 narrateur|Elle enfile trop vite, un bouton saute.
 narrateur|La poignée froide lui pique la paume, trop nue.
-papa|Le bouton d'abord, ensuite le bois.
+papa|Le bouton a sauté, le bois peut attendre.
 maman|La laine tiédit tes épaules, et tes mains.
 enfant-f|Le bouton m'a échappé !
 narrateur|Elle le retrouve, sous la chaise, sans courir.
@@ -5890,17 +5890,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le sac dans la poche, et ça a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. La poche du gilet garde une plume, collée au sac.</t>
+          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le sac dans la poche, et ça a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. La poche a gardé l'oiseau, au chaud. La poche du gilet garde une plume, collée au sac.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le sac dans la poche, et ça a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. La poche du gilet garde une plume, collée au sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le sac dans la poche, et ça a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. La poche a gardé l'oiseau, au chaud. La poche du gilet garde une plume, collée au sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le sac dans la poche, et ça a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. La poche du gilet garde une plume, collée au sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le sac dans la poche, et ça a ouvert. Sur la chaise de la chambre, le linge s'est tu. À table, le pain casse, tiède, sous les doigts. La poche a gardé l'oiseau, au chaud. La poche du gilet garde une plume, collée au sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -6039,7 +6039,7 @@
 enfant-f|J'ai mis le gilet, le sac dans la poche, et ça a ouvert.
 narrateur|Sur la chaise de la chambre, le linge s'est tu.
 narrateur|À table, le pain casse, tiède, sous les doigts.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|La poche a gardé l'oiseau, au chaud.
 narrateur|La poche du gilet garde une plume, collée au sac.</t>
         </is>
       </c>
@@ -6256,17 +6256,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le manteau, deux chaleurs. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau et le gilet se touchent, chauds, devant le vide.</t>
+          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le manteau, deux chaleurs. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Deux tissus, et tu ne grelottes plus. Le manteau et le gilet se touchent, chauds, devant le vide.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le manteau, deux chaleurs. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau et le gilet se touchent, chauds, devant le vide.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le manteau, deux chaleurs. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Deux tissus, et tu ne grelottes plus. Le manteau et le gilet se touchent, chauds, devant le vide.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le manteau, deux chaleurs. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau et le gilet se touchent, chauds, devant le vide.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le manteau, deux chaleurs. Sur la chaise de la chambre, le linge s'est tu. À table, une goutte de lait fait un rond. Deux tissus, et tu ne grelottes plus. Le manteau et le gilet se touchent, chauds, devant le vide.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -6405,7 +6405,7 @@
 enfant-f|J'ai mis le gilet, le manteau, deux chaleurs.
 narrateur|Sur la chaise de la chambre, le linge s'est tu.
 narrateur|À table, une goutte de lait fait un rond.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Deux tissus, et tu ne grelottes plus.
 narrateur|Le manteau et le gilet se touchent, chauds, devant le vide.</t>
         </is>
       </c>
@@ -6622,17 +6622,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le doudou dans la poche. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou s'endort dans le gilet, le volet ouvert.</t>
+          <t>Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le doudou dans la poche. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Ils se sont endormis dans la laine. Le doudou s'endort dans le gilet, le volet ouvert.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le doudou dans la poche. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou s'endort dans le gilet, le &lt;emphasis level="moderate"&gt;volet&lt;/emphasis&gt; ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le doudou dans la poche. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Ils se sont endormis dans la laine. Le doudou s'endort dans le gilet, le &lt;emphasis level="moderate"&gt;volet&lt;/emphasis&gt; ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le doudou dans la poche. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou s'endort dans le gilet, le &lt;emphasis&gt;volet&lt;/emphasis&gt; ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Raconte, Victorina, on t'écoute. J'ai mis le gilet, le doudou dans la poche. Sur la chaise de la chambre, le linge s'est tu. À table, le moineau chante, trop loin pour le bol. Ils se sont endormis dans la laine. Le doudou s'endort dans le gilet, le &lt;emphasis&gt;volet&lt;/emphasis&gt; ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -6775,7 +6775,7 @@
 enfant-f|J'ai mis le gilet, le doudou dans la poche.
 narrateur|Sur la chaise de la chambre, le linge s'est tu.
 narrateur|À table, le moineau chante, trop loin pour le bol.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Ils se sont endormis dans la laine.
 narrateur|Le doudou s'endort dans le gilet, le volet ouvert.</t>
         </is>
       </c>
@@ -8129,17 +8129,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai séché mes mains, le t-shirt, le sac a pris l'oiseau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Dans le sac, l'oiseau sent le savon, et le vent.</t>
+          <t>Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai séché mes mains, le t-shirt, le sac a pris l'oiseau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tes mains ont tenu, sèches, cette fois. Dans le sac, l'oiseau sent le savon, et le vent.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai séché mes mains, le t-shirt, le sac a pris l'oiseau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Dans le sac, l'oiseau sent le savon, et le vent.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai séché mes mains, le t-shirt, le sac a pris l'oiseau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tes mains ont tenu, sèches, cette fois. Dans le sac, l'oiseau sent le savon, et le vent.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai séché mes mains, le t-shirt, le sac a pris l'oiseau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Dans le sac, l'oiseau sent le savon, et le vent.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai séché mes mains, le t-shirt, le sac a pris l'oiseau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tes mains ont tenu, sèches, cette fois. Dans le sac, l'oiseau sent le savon, et le vent.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -8273,12 +8273,12 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, une miette roule vers le bol.
 maman|Dis-nous, le pain est prêt.
 enfant-f|J'ai séché mes mains, le t-shirt, le sac a pris l'oiseau.
 narrateur|Dans la salle d'eau, le miroir n'a plus d'œil de buée.
 narrateur|À table, le pain casse, tiède, sous les doigts.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Tes mains ont tenu, sèches, cette fois.
 narrateur|Dans le sac, l'oiseau sent le savon, et le vent.</t>
         </is>
       </c>
@@ -8495,17 +8495,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le manteau a bu la goutte. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau sèche une goutte, près de la poignée.</t>
+          <t>Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le manteau a bu la goutte. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Le manteau a bu la goutte, toi. Le manteau sèche une goutte, près de la poignée.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le manteau a bu la goutte. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau sèche une goutte, près de la poignée.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le manteau a bu la goutte. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Le manteau a bu la goutte, toi. Le manteau sèche une goutte, près de la poignée.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le manteau a bu la goutte. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau sèche une goutte, près de la poignée.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le manteau a bu la goutte. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Le manteau a bu la goutte, toi. Le manteau sèche une goutte, près de la poignée.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -8639,12 +8639,12 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, une miette roule vers le bol.
 maman|Dis-nous, le pain est prêt.
 enfant-f|J'ai séché, le t-shirt, le manteau a bu la goutte.
 narrateur|Dans la salle d'eau, le miroir n'a plus d'œil de buée.
 narrateur|À table, une goutte de lait fait un rond.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le manteau a bu la goutte, toi.
 narrateur|Le manteau sèche une goutte, près de la poignée.</t>
         </is>
       </c>
@@ -8861,17 +8861,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le doudou n'a pas eu d'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou a les joues humides, et il rit vers la rue.</t>
+          <t>Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le doudou n'a pas eu d'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Le doudou n'a pas eu d'eau. Le doudou a les joues humides, et il rit vers la rue.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le doudou n'a pas eu d'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou a les joues humides, et il rit vers la rue.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le doudou n'a pas eu d'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Le doudou n'a pas eu d'eau. Le doudou a les joues humides, et il rit vers la rue.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le doudou n'a pas eu d'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou a les joues humides, et il rit vers la rue.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai séché, le t-shirt, le doudou n'a pas eu d'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Le doudou n'a pas eu d'eau. Le doudou a les joues humides, et il rit vers la rue.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -9005,12 +9005,12 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, une miette roule vers le bol.
 maman|Dis-nous, le pain est prêt.
 enfant-f|J'ai séché, le t-shirt, le doudou n'a pas eu d'eau.
 narrateur|Dans la salle d'eau, le miroir n'a plus d'œil de buée.
 narrateur|À table, le moineau chante, trop loin pour le bol.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le doudou n'a pas eu d'eau.
 narrateur|Le doudou a les joues humides, et il rit vers la rue.</t>
         </is>
       </c>
@@ -9615,17 +9615,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis les chaussettes sèches, le sac sous la poignée. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Une chaussette laisse une trace ronde, sous le sac.</t>
+          <t>Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis les chaussettes sèches, le sac sous la poignée. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. La trace ronde, c'est ta chaussette. Une chaussette laisse une trace ronde, sous le sac.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis les chaussettes sèches, le sac sous la poignée. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Une chaussette laisse une trace ronde, sous le sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis les chaussettes sèches, le sac sous la poignée. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. La trace ronde, c'est ta chaussette. Une chaussette laisse une trace ronde, sous le sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis les chaussettes sèches, le sac sous la poignée. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Une chaussette laisse une trace ronde, sous le sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis les chaussettes sèches, le sac sous la poignée. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. La trace ronde, c'est ta chaussette. Une chaussette laisse une trace ronde, sous le sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -9759,12 +9759,12 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, une miette roule vers le bol.
 maman|Dis-nous, le pain est prêt.
 enfant-f|J'ai mis les chaussettes sèches, le sac sous la poignée.
 narrateur|Dans la salle d'eau, le miroir n'a plus d'œil de buée.
 narrateur|À table, le pain casse, tiède, sous les doigts.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|La trace ronde, c'est ta chaussette.
 narrateur|Une chaussette laisse une trace ronde, sous le sac.</t>
         </is>
       </c>
@@ -9981,17 +9981,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le manteau, sans sauter. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau sent le savon, et la rue entre.</t>
+          <t>Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le manteau, sans sauter. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu es restée droite, près du bois. Le manteau sent le savon, et la rue entre.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le manteau, sans sauter. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau sent le savon, et la rue entre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le manteau, sans sauter. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu es restée droite, près du bois. Le manteau sent le savon, et la rue entre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le manteau, sans sauter. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau sent le savon, et la rue entre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le manteau, sans sauter. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu es restée droite, près du bois. Le manteau sent le savon, et la rue entre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -10125,12 +10125,12 @@
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, une miette roule vers le bol.
 maman|Dis-nous, le pain est prêt.
 enfant-f|J'ai mis les chaussettes, le manteau, sans sauter.
 narrateur|Dans la salle d'eau, le miroir n'a plus d'œil de buée.
 narrateur|À table, une goutte de lait fait un rond.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Tu es restée droite, près du bois.
 narrateur|Le manteau sent le savon, et la rue entre.</t>
         </is>
       </c>
@@ -10347,17 +10347,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le doudou loin des gouttes. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, les pieds au chaud, voit le moineau.</t>
+          <t>Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le doudou loin des gouttes. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Le doudou a vu le moineau, au sec. Le doudou, les pieds au chaud, voit le moineau.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le doudou loin des gouttes. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, les pieds au chaud, voit le moineau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le doudou loin des gouttes. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Le doudou a vu le moineau, au sec. Le doudou, les pieds au chaud, voit le moineau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le doudou loin des gouttes. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, les pieds au chaud, voit le moineau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis les chaussettes, le doudou loin des gouttes. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Le doudou a vu le moineau, au sec. Le doudou, les pieds au chaud, voit le moineau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -10491,12 +10491,12 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, une miette roule vers le bol.
 maman|Dis-nous, le pain est prêt.
 enfant-f|J'ai mis les chaussettes, le doudou loin des gouttes.
 narrateur|Dans la salle d'eau, le miroir n'a plus d'œil de buée.
 narrateur|À table, le moineau chante, trop loin pour le bol.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le doudou a vu le moineau, au sec.
 narrateur|Le doudou, les pieds au chaud, voit le moineau.</t>
         </is>
       </c>
@@ -10529,17 +10529,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Ses mains sentent le savon, plus sèches, plus prêtes. Victorina prend le gilet, près de la buée. Je le mets, et je repars ! La laine accroche une goutte, trop pressée. Un bouton reste ouvert, face au miroir. Le bouton d'abord, la poignée ensuite. La laine mouillée pique, comme le savon. Il me tient le ventre, tout ouvert ! Elle s'arrête, et le bouton rentre, net. Le gilet sent le savon, et un peu de laine. Tes épaules sont prêtes, pour le bois. J'ai la laine, et après ?</t>
+          <t>Ses mains sentent le savon, plus sèches, plus prêtes. Victorina prend le gilet, près de la buée. Je le mets, et je repars ! La laine accroche une goutte, trop pressée. Un bouton reste ouvert, face au miroir. Le bouton est ouvert, face au miroir. La laine mouillée pique, comme le savon. Il me tient le ventre, tout ouvert ! Elle s'arrête, et le bouton rentre, net. Le gilet sent le savon, et un peu de laine. Tes épaules sont prêtes, pour le bois. J'ai la laine, et après ?</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Ses mains sentent le savon, plus sèches, plus prêtes. Victorina prend le &lt;emphasis level="moderate"&gt;gilet&lt;/emphasis&gt;, près de la buée. Je le mets, et je repars ! La laine accroche une goutte, trop pressée. Un bouton reste ouvert, face au miroir. Le bouton d'abord, la poignée ensuite. La laine mouillée pique, comme le savon. Il me tient le ventre, tout ouvert ! Elle s'arrête, et le bouton rentre, net. Le gilet sent le savon, et un peu de laine. Tes épaules sont prêtes, pour le bois. J'ai la laine, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Ses mains sentent le savon, plus sèches, plus prêtes. Victorina prend le &lt;emphasis level="moderate"&gt;gilet&lt;/emphasis&gt;, près de la buée. Je le mets, et je repars ! La laine accroche une goutte, trop pressée. Un bouton reste ouvert, face au miroir. Le bouton est ouvert, face au miroir. La laine mouillée pique, comme le savon. Il me tient le ventre, tout ouvert ! Elle s'arrête, et le bouton rentre, net. Le gilet sent le savon, et un peu de laine. Tes épaules sont prêtes, pour le bois. J'ai la laine, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Ses mains sentent le savon, plus sèches, plus prêtes. Victorina prend le &lt;emphasis&gt;gilet&lt;/emphasis&gt;, près de la buée. Je le mets, et je repars ! La laine accroche une goutte, trop pressée. Un bouton reste ouvert, face au miroir. Le bouton d'abord, la poignée ensuite. La laine mouillée pique, comme le savon. Il me tient le ventre, tout ouvert ! Elle s'arrête, et le bouton rentre, net. Le gilet sent le savon, et un peu de laine. Tes épaules sont prêtes, pour le bois. J'ai la laine, et après ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Ses mains sentent le savon, plus sèches, plus prêtes. Victorina prend le &lt;emphasis&gt;gilet&lt;/emphasis&gt;, près de la buée. Je le mets, et je repars ! La laine accroche une goutte, trop pressée. Un bouton reste ouvert, face au miroir. Le bouton est ouvert, face au miroir. La laine mouillée pique, comme le savon. Il me tient le ventre, tout ouvert ! Elle s'arrête, et le bouton rentre, net. Le gilet sent le savon, et un peu de laine. Tes épaules sont prêtes, pour le bois. J'ai la laine, et après ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -10682,7 +10682,7 @@
 enfant-f|Je le mets, et je repars !
 narrateur|La laine accroche une goutte, trop pressée.
 narrateur|Un bouton reste ouvert, face au miroir.
-maman|Le bouton d'abord, la poignée ensuite.
+maman|Le bouton est ouvert, face au miroir.
 papa|La laine mouillée pique, comme le savon.
 enfant-f|Il me tient le ventre, tout ouvert !
 narrateur|Elle s'arrête, et le bouton rentre, net.
@@ -11100,17 +11100,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis le gilet, le sac au sec, loin de l'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. La poche du gilet sent le savon, près du sac.</t>
+          <t>Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis le gilet, le sac au sec, loin de l'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. La poche sent le savon, et le vent. La poche du gilet sent le savon, près du sac.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis le gilet, le sac au sec, loin de l'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. La poche du gilet sent le savon, près du sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis le gilet, le sac au sec, loin de l'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. La poche sent le savon, et le vent. La poche du gilet sent le savon, près du sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis le gilet, le sac au sec, loin de l'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. La poche du gilet sent le savon, près du sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis le gilet, le sac au sec, loin de l'eau. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le pain casse, tiède, sous les doigts. La poche sent le savon, et le vent. La poche du gilet sent le savon, près du sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -11244,12 +11244,12 @@
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, une miette roule vers le bol.
 maman|Dis-nous, le pain est prêt.
 enfant-f|J'ai mis le gilet, le sac au sec, loin de l'eau.
 narrateur|Dans la salle d'eau, le miroir n'a plus d'œil de buée.
 narrateur|À table, le pain casse, tiède, sous les doigts.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|La poche sent le savon, et le vent.
 narrateur|La poche du gilet sent le savon, près du sac.</t>
         </is>
       </c>
@@ -11465,17 +11465,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis le gilet, le manteau a boutonné. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau boutonne le gilet, face au soleil.</t>
+          <t>Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis le gilet, le manteau a boutonné. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Le bouton du manteau a fait le reste. Le manteau boutonne le gilet, face au soleil.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis le gilet, le manteau a boutonné. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau boutonne le gilet, face au soleil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis le gilet, le manteau a boutonné. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Le bouton du manteau a fait le reste. Le manteau boutonne le gilet, face au soleil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis le gilet, le manteau a boutonné. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau boutonne le gilet, face au soleil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis le gilet, le manteau a boutonné. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, une goutte de lait fait un rond. Le bouton du manteau a fait le reste. Le manteau boutonne le gilet, face au soleil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11609,12 +11609,12 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, une miette roule vers le bol.
 maman|Dis-nous, le pain est prêt.
 enfant-f|J'ai mis le gilet, le manteau a boutonné.
 narrateur|Dans la salle d'eau, le miroir n'a plus d'œil de buée.
 narrateur|À table, une goutte de lait fait un rond.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le bouton du manteau a fait le reste.
 narrateur|Le manteau boutonne le gilet, face au soleil.</t>
         </is>
       </c>
@@ -11830,17 +11830,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis le gilet, le doudou sous le toit de laine. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou s'abrite dans le gilet, le bois ouvert.</t>
+          <t>Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis le gilet, le doudou sous le toit de laine. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Le gilet a fait un toit, pour lui. Le doudou s'abrite dans le gilet, le bois ouvert.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis le gilet, le doudou sous le toit de laine. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou s'abrite dans le gilet, le bois ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis le gilet, le doudou sous le toit de laine. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Le gilet a fait un toit, pour lui. Le doudou s'abrite dans le gilet, le bois ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. Dis-nous, le pain est prêt. J'ai mis le gilet, le doudou sous le toit de laine. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou s'abrite dans le gilet, le bois ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, une miette roule vers le bol. Dis-nous, le pain est prêt. J'ai mis le gilet, le doudou sous le toit de laine. Dans la salle d'eau, le miroir n'a plus d'œil de buée. À table, le moineau chante, trop loin pour le bol. Le gilet a fait un toit, pour lui. Le doudou s'abrite dans le gilet, le bois ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -11974,12 +11974,12 @@
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, une miette roule vers le bol.
 maman|Dis-nous, le pain est prêt.
 enfant-f|J'ai mis le gilet, le doudou sous le toit de laine.
 narrateur|Dans la salle d'eau, le miroir n'a plus d'œil de buée.
 narrateur|À table, le moineau chante, trop loin pour le bol.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le gilet a fait un toit, pour lui.
 narrateur|Le doudou s'abrite dans le gilet, le bois ouvert.</t>
         </is>
       </c>
@@ -12761,17 +12761,17 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le t-shirt, près du four. Je le mets, et je prends l'huile ! Elle enfile trop vite, le coton se tord. Une manche frôle le bol, trop près de l'huile. Le bras d'abord, le bol ensuite. Le pain dore, et toi, tu grelottes moins. La manche a failli tout tacher ! Elle ralentit, et le t-shirt tombe droit. Le coton garde un peu de chaleur du four. Avec ça, tu peux porter l'huile. J'ai le coton, et après ?</t>
+          <t>L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le t-shirt, près du four. Je le mets, et je prends l'huile ! Elle enfile trop vite, le coton se tord. Une manche frôle le bol, trop près de l'huile. Le bol est trop près, sors le bras. Le pain dore, et toi, tu grelottes moins. La manche a failli tout tacher ! Elle ralentit, et le t-shirt tombe droit. Le coton garde un peu de chaleur du four. Avec ça, tu peux porter l'huile. J'ai le coton, et après ?</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le &lt;emphasis level="moderate"&gt;t-shirt&lt;/emphasis&gt;, près du four. Je le mets, et je prends l'huile ! Elle enfile trop vite, le coton se tord. Une manche frôle le bol, trop près de l'huile. Le bras d'abord, le bol ensuite. Le pain dore, et toi, tu grelottes moins. La manche a failli tout tacher ! Elle ralentit, et le t-shirt tombe droit. Le coton garde un peu de chaleur du four. Avec ça, tu peux porter l'huile. J'ai le coton, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le &lt;emphasis level="moderate"&gt;t-shirt&lt;/emphasis&gt;, près du four. Je le mets, et je prends l'huile ! Elle enfile trop vite, le coton se tord. Une manche frôle le bol, trop près de l'huile. Le bol est trop près, sors le bras. Le pain dore, et toi, tu grelottes moins. La manche a failli tout tacher ! Elle ralentit, et le t-shirt tombe droit. Le coton garde un peu de chaleur du four. Avec ça, tu peux porter l'huile. J'ai le coton, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le &lt;emphasis&gt;t-shirt&lt;/emphasis&gt;, près du four. Je le mets, et je prends l'huile ! Elle enfile trop vite, le coton se tord. Une manche frôle le bol, trop près de l'huile. Le bras d'abord, le bol ensuite. Le pain dore, et toi, tu grelottes moins. La manche a failli tout tacher ! Elle ralentit, et le t-shirt tombe droit. Le coton garde un peu de chaleur du four. Avec ça, tu peux porter l'huile. J'ai le coton, et après ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le &lt;emphasis&gt;t-shirt&lt;/emphasis&gt;, près du four. Je le mets, et je prends l'huile ! Elle enfile trop vite, le coton se tord. Une manche frôle le bol, trop près de l'huile. Le bol est trop près, sors le bras. Le pain dore, et toi, tu grelottes moins. La manche a failli tout tacher ! Elle ralentit, et le t-shirt tombe droit. Le coton garde un peu de chaleur du four. Avec ça, tu peux porter l'huile. J'ai le coton, et après ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -12914,7 +12914,7 @@
 enfant-f|Je le mets, et je prends l'huile !
 narrateur|Elle enfile trop vite, le coton se tord.
 narrateur|Une manche frôle le bol, trop près de l'huile.
-papa|Le bras d'abord, le bol ensuite.
+papa|Le bol est trop près, sors le bras.
 maman|Le pain dore, et toi, tu grelottes moins.
 enfant-f|La manche a failli tout tacher !
 narrateur|Elle ralentit, et le t-shirt tombe droit.
@@ -13333,17 +13333,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le t-shirt, le sac a l'huile et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Le sac, près du bol, garde l'oiseau et une miette.</t>
+          <t>Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le t-shirt, le sac a l'huile et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. L'huile a parlé au bois, sans bruit. Le sac, près du bol, garde l'oiseau et une miette.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le t-shirt, le sac a l'huile et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Le sac, près du bol, garde l'oiseau et une miette.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le t-shirt, le sac a l'huile et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. L'huile a parlé au bois, sans bruit. Le sac, près du bol, garde l'oiseau et une miette.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le t-shirt, le sac a l'huile et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Le sac, près du bol, garde l'oiseau et une miette.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le t-shirt, le sac a l'huile et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. L'huile a parlé au bois, sans bruit. Le sac, près du bol, garde l'oiseau et une miette.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -13477,12 +13477,12 @@
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, le four s'est tu, et le pain fume.
 maman|À toi, on a fini nos phrases.
 enfant-f|J'ai mis le t-shirt, le sac a l'huile et l'oiseau.
 narrateur|Sur la table, le pain fume, une miette à part.
 narrateur|À table, le pain casse, tiède, sous les doigts.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|L'huile a parlé au bois, sans bruit.
 narrateur|Le sac, près du bol, garde l'oiseau et une miette.</t>
         </is>
       </c>
@@ -13699,17 +13699,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le t-shirt, le manteau, et le pain a vu la rue. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau, près du pain, tient un fil de soleil.</t>
+          <t>Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le t-shirt, le manteau, et le pain a vu la rue. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Le pain a vu la rue, avec toi. Le manteau, près du pain, tient un fil de soleil.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le t-shirt, le manteau, et le pain a vu la rue. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau, près du pain, tient un fil de soleil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le t-shirt, le manteau, et le pain a vu la rue. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Le pain a vu la rue, avec toi. Le manteau, près du pain, tient un fil de soleil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le t-shirt, le manteau, et le pain a vu la rue. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau, près du pain, tient un fil de soleil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le t-shirt, le manteau, et le pain a vu la rue. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Le pain a vu la rue, avec toi. Le manteau, près du pain, tient un fil de soleil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -13843,12 +13843,12 @@
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, le four s'est tu, et le pain fume.
 maman|À toi, on a fini nos phrases.
 enfant-f|J'ai mis le t-shirt, le manteau, et le pain a vu la rue.
 narrateur|Sur la table, le pain fume, une miette à part.
 narrateur|À table, une goutte de lait fait un rond.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le pain a vu la rue, avec toi.
 narrateur|Le manteau, près du pain, tient un fil de soleil.</t>
         </is>
       </c>
@@ -14065,17 +14065,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le t-shirt, le doudou a le four et la rue. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, près du four, regarde le volet ouvert.</t>
+          <t>Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le t-shirt, le doudou a le four et la rue. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Il a deux odeurs, le doudou. Le doudou, près du four, regarde le volet ouvert.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le t-shirt, le doudou a le four et la rue. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, près du four, regarde le &lt;emphasis level="moderate"&gt;volet&lt;/emphasis&gt; ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le t-shirt, le doudou a le four et la rue. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Il a deux odeurs, le doudou. Le doudou, près du four, regarde le &lt;emphasis level="moderate"&gt;volet&lt;/emphasis&gt; ouvert.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le t-shirt, le doudou a le four et la rue. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, près du four, regarde le &lt;emphasis&gt;volet&lt;/emphasis&gt; ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le t-shirt, le doudou a le four et la rue. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Il a deux odeurs, le doudou. Le doudou, près du four, regarde le &lt;emphasis&gt;volet&lt;/emphasis&gt; ouvert.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -14213,12 +14213,12 @@
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, le four s'est tu, et le pain fume.
 maman|À toi, on a fini nos phrases.
 enfant-f|J'ai mis le t-shirt, le doudou a le four et la rue.
 narrateur|Sur la table, le pain fume, une miette à part.
 narrateur|À table, le moineau chante, trop loin pour le bol.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Il a deux odeurs, le doudou.
 narrateur|Le doudou, près du four, regarde le volet ouvert.</t>
         </is>
       </c>
@@ -14251,17 +14251,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend les chaussettes, sous la table. Je les mets, et je prends l'huile ! Elle enfile trop vite, un talon reste plié. Sur les carreaux, le talon plié la fait pencher. Le talon d'abord, l'huile ensuite. Les carreaux piquent moins, avec ça. Mon talon me chatouille ! Elle s'assoit, et le talon se déplie, net. Les deux chaussettes tiennent, chaudes, sous la table. Avec ça, tu peux porter l'huile. J'ai les deux, et après ?</t>
+          <t>L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend les chaussettes, sous la table. Je les mets, et je prends l'huile ! Elle enfile trop vite, un talon reste plié. Sur les carreaux, le talon plié la fait pencher. Ton talon est plié, l'huile attend. Les carreaux piquent moins, avec ça. Mon talon me chatouille ! Elle s'assoit, et le talon se déplie, net. Les deux chaussettes tiennent, chaudes, sous la table. Avec ça, tu peux porter l'huile. J'ai les deux, et après ?</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend les &lt;emphasis level="moderate"&gt;chaussettes&lt;/emphasis&gt;, sous la table. Je les mets, et je prends l'huile ! Elle enfile trop vite, un talon reste plié. Sur les carreaux, le talon plié la fait pencher. Le talon d'abord, l'huile ensuite. Les carreaux piquent moins, avec ça. Mon talon me chatouille ! Elle s'assoit, et le talon se déplie, net. Les deux chaussettes tiennent, chaudes, sous la table. Avec ça, tu peux porter l'huile. J'ai les deux, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend les &lt;emphasis level="moderate"&gt;chaussettes&lt;/emphasis&gt;, sous la table. Je les mets, et je prends l'huile ! Elle enfile trop vite, un talon reste plié. Sur les carreaux, le talon plié la fait pencher. Ton talon est plié, l'huile attend. Les carreaux piquent moins, avec ça. Mon talon me chatouille ! Elle s'assoit, et le talon se déplie, net. Les deux chaussettes tiennent, chaudes, sous la table. Avec ça, tu peux porter l'huile. J'ai les deux, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend les &lt;emphasis&gt;chaussettes&lt;/emphasis&gt;, sous la table. Je les mets, et je prends l'huile ! Elle enfile trop vite, un talon reste plié. Sur les carreaux, le talon plié la fait pencher. Le talon d'abord, l'huile ensuite. Les carreaux piquent moins, avec ça. Mon talon me chatouille ! Elle s'assoit, et le talon se déplie, net. Les deux chaussettes tiennent, chaudes, sous la table. Avec ça, tu peux porter l'huile. J'ai les deux, et après ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend les &lt;emphasis&gt;chaussettes&lt;/emphasis&gt;, sous la table. Je les mets, et je prends l'huile ! Elle enfile trop vite, un talon reste plié. Sur les carreaux, le talon plié la fait pencher. Ton talon est plié, l'huile attend. Les carreaux piquent moins, avec ça. Mon talon me chatouille ! Elle s'assoit, et le talon se déplie, net. Les deux chaussettes tiennent, chaudes, sous la table. Avec ça, tu peux porter l'huile. J'ai les deux, et après ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -14404,7 +14404,7 @@
 enfant-f|Je les mets, et je prends l'huile !
 narrateur|Elle enfile trop vite, un talon reste plié.
 narrateur|Sur les carreaux, le talon plié la fait pencher.
-papa|Le talon d'abord, l'huile ensuite.
+papa|Ton talon est plié, l'huile attend.
 maman|Les carreaux piquent moins, avec ça.
 enfant-f|Mon talon me chatouille !
 narrateur|Elle s'assoit, et le talon se déplie, net.
@@ -14822,17 +14822,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis les chaussettes, le sac près du bol. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Les chaussettes, sous la table, sentent le pain chaud.</t>
+          <t>Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis les chaussettes, le sac près du bol. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Les carreaux n'ont plus piqué tes pieds. Les chaussettes, sous la table, sentent le pain chaud.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis les chaussettes, le sac près du bol. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Les chaussettes, sous la table, sentent le pain chaud.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis les chaussettes, le sac près du bol. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Les carreaux n'ont plus piqué tes pieds. Les chaussettes, sous la table, sentent le pain chaud.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis les chaussettes, le sac près du bol. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. Les chaussettes, sous la table, sentent le pain chaud.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis les chaussettes, le sac près du bol. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Les carreaux n'ont plus piqué tes pieds. Les chaussettes, sous la table, sentent le pain chaud.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -14966,12 +14966,12 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, le four s'est tu, et le pain fume.
 maman|À toi, on a fini nos phrases.
 enfant-f|J'ai mis les chaussettes, le sac près du bol.
 narrateur|Sur la table, le pain fume, une miette à part.
 narrateur|À table, le pain casse, tiède, sous les doigts.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Les carreaux n'ont plus piqué tes pieds.
 narrateur|Les chaussettes, sous la table, sentent le pain chaud.</t>
         </is>
       </c>
@@ -15188,17 +15188,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis les chaussettes, le manteau, pour le pain dehors. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau, sur la chaise de cuisine, garde le vent.</t>
+          <t>Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis les chaussettes, le manteau, pour le pain dehors. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Le manteau gardera le vent, en bas. Le manteau, sur la chaise de cuisine, garde le vent.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis les chaussettes, le manteau, pour le pain dehors. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau, sur la chaise de cuisine, garde le vent.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis les chaussettes, le manteau, pour le pain dehors. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Le manteau gardera le vent, en bas. Le manteau, sur la chaise de cuisine, garde le vent.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis les chaussettes, le manteau, pour le pain dehors. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau, sur la chaise de cuisine, garde le vent.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis les chaussettes, le manteau, pour le pain dehors. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Le manteau gardera le vent, en bas. Le manteau, sur la chaise de cuisine, garde le vent.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -15332,12 +15332,12 @@
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, le four s'est tu, et le pain fume.
 maman|À toi, on a fini nos phrases.
 enfant-f|J'ai mis les chaussettes, le manteau, pour le pain dehors.
 narrateur|Sur la table, le pain fume, une miette à part.
 narrateur|À table, une goutte de lait fait un rond.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le manteau gardera le vent, en bas.
 narrateur|Le manteau, sur la chaise de cuisine, garde le vent.</t>
         </is>
       </c>
@@ -15553,17 +15553,17 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis les chaussettes, le doudou a une miette. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou a une miette sur le nez, et la rue.</t>
+          <t>Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis les chaussettes, le doudou a une miette. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Il a une miette, et la rue. Le doudou a une miette sur le nez, et la rue.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis les chaussettes, le doudou a une miette. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou a une miette sur le nez, et la rue.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis les chaussettes, le doudou a une miette. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Il a une miette, et la rue. Le doudou a une miette sur le nez, et la rue.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis les chaussettes, le doudou a une miette. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou a une miette sur le nez, et la rue.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis les chaussettes, le doudou a une miette. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Il a une miette, et la rue. Le doudou a une miette sur le nez, et la rue.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -15697,12 +15697,12 @@
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, le four s'est tu, et le pain fume.
 maman|À toi, on a fini nos phrases.
 enfant-f|J'ai mis les chaussettes, le doudou a une miette.
 narrateur|Sur la table, le pain fume, une miette à part.
 narrateur|À table, le moineau chante, trop loin pour le bol.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Il a une miette, et la rue.
 narrateur|Le doudou a une miette sur le nez, et la rue.</t>
         </is>
       </c>
@@ -15735,17 +15735,17 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le gilet, près du four tiède. Je le mets, et je prends l'huile ! Elle enfile trop vite, la poche se retourne. L'huile frôle la laine, trop près du bol. La poche d'abord, le bol ensuite. La laine tiédit, comme le pain. La poche voulait tout avaler ! Elle la remet, sans toucher l'huile. Le gilet ferme, et une poche attend, nette. Avec ça, tu peux porter l'huile. J'ai la laine, et après ?</t>
+          <t>L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le gilet, près du four tiède. Je le mets, et je prends l'huile ! Elle enfile trop vite, la poche se retourne. L'huile frôle la laine, trop près du bol. La poche est à l'envers, loin du bol. La laine tiédit, comme le pain. La poche voulait tout avaler ! Elle la remet, sans toucher l'huile. Le gilet ferme, et une poche attend, nette. Avec ça, tu peux porter l'huile. J'ai la laine, et après ?</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le &lt;emphasis level="moderate"&gt;gilet&lt;/emphasis&gt;, près du four tiède. Je le mets, et je prends l'huile ! Elle enfile trop vite, la poche se retourne. L'huile frôle la laine, trop près du bol. La poche d'abord, le bol ensuite. La laine tiédit, comme le pain. La poche voulait tout avaler ! Elle la remet, sans toucher l'huile. Le gilet ferme, et une poche attend, nette. Avec ça, tu peux porter l'huile. J'ai la laine, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le &lt;emphasis level="moderate"&gt;gilet&lt;/emphasis&gt;, près du four tiède. Je le mets, et je prends l'huile ! Elle enfile trop vite, la poche se retourne. L'huile frôle la laine, trop près du bol. La poche est à l'envers, loin du bol. La laine tiédit, comme le pain. La poche voulait tout avaler ! Elle la remet, sans toucher l'huile. Le gilet ferme, et une poche attend, nette. Avec ça, tu peux porter l'huile. J'ai la laine, et après ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le &lt;emphasis&gt;gilet&lt;/emphasis&gt;, près du four tiède. Je le mets, et je prends l'huile ! Elle enfile trop vite, la poche se retourne. L'huile frôle la laine, trop près du bol. La poche d'abord, le bol ensuite. La laine tiédit, comme le pain. La poche voulait tout avaler ! Elle la remet, sans toucher l'huile. Le gilet ferme, et une poche attend, nette. Avec ça, tu peux porter l'huile. J'ai la laine, et après ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;L'odeur du pain suit ses pas, jusque sous le bois. Victorina prend le &lt;emphasis&gt;gilet&lt;/emphasis&gt;, près du four tiède. Je le mets, et je prends l'huile ! Elle enfile trop vite, la poche se retourne. L'huile frôle la laine, trop près du bol. La poche est à l'envers, loin du bol. La laine tiédit, comme le pain. La poche voulait tout avaler ! Elle la remet, sans toucher l'huile. Le gilet ferme, et une poche attend, nette. Avec ça, tu peux porter l'huile. J'ai la laine, et après ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -15888,7 +15888,7 @@
 enfant-f|Je le mets, et je prends l'huile !
 narrateur|Elle enfile trop vite, la poche se retourne.
 narrateur|L'huile frôle la laine, trop près du bol.
-papa|La poche d'abord, le bol ensuite.
+papa|La poche est à l'envers, loin du bol.
 maman|La laine tiédit, comme le pain.
 enfant-f|La poche voulait tout avaler !
 narrateur|Elle la remet, sans toucher l'huile.
@@ -16306,17 +16306,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le gilet, le sac a une miette et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. La poche du gilet tient une miette, et l'oiseau.</t>
+          <t>Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le gilet, le sac a une miette et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. La poche a fait le voyage, toi. La poche du gilet tient une miette, et l'oiseau.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le gilet, le sac a une miette et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. La poche du gilet tient une miette, et l'oiseau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le gilet, le sac a une miette et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. La poche a fait le voyage, toi. La poche du gilet tient une miette, et l'oiseau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le gilet, le sac a une miette et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. Tu as ouvert, sans tout tirer d'un coup. La poche du gilet tient une miette, et l'oiseau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le gilet, le sac a une miette et l'oiseau. Sur la table, le pain fume, une miette à part. À table, le pain casse, tiède, sous les doigts. La poche a fait le voyage, toi. La poche du gilet tient une miette, et l'oiseau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -16450,12 +16450,12 @@
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, le four s'est tu, et le pain fume.
 maman|À toi, on a fini nos phrases.
 enfant-f|J'ai mis le gilet, le sac a une miette et l'oiseau.
 narrateur|Sur la table, le pain fume, une miette à part.
 narrateur|À table, le pain casse, tiède, sous les doigts.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|La poche a fait le voyage, toi.
 narrateur|La poche du gilet tient une miette, et l'oiseau.</t>
         </is>
       </c>
@@ -16671,17 +16671,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le gilet, le manteau, on sentait le four. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau et le gilet, près du four, sentent le pain.</t>
+          <t>Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le gilet, le manteau, on sentait le four. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Le four a prêté sa chaleur. Le manteau et le gilet, près du four, sentent le pain.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le gilet, le manteau, on sentait le four. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau et le gilet, près du four, sentent le pain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le gilet, le manteau, on sentait le four. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Le four a prêté sa chaleur. Le manteau et le gilet, près du four, sentent le pain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le gilet, le manteau, on sentait le four. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Tu as ouvert, sans tout tirer d'un coup. Le manteau et le gilet, près du four, sentent le pain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le gilet, le manteau, on sentait le four. Sur la table, le pain fume, une miette à part. À table, une goutte de lait fait un rond. Le four a prêté sa chaleur. Le manteau et le gilet, près du four, sentent le pain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -16815,12 +16815,12 @@
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, le four s'est tu, et le pain fume.
 maman|À toi, on a fini nos phrases.
 enfant-f|J'ai mis le gilet, le manteau, on sentait le four.
 narrateur|Sur la table, le pain fume, une miette à part.
 narrateur|À table, une goutte de lait fait un rond.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Le four a prêté sa chaleur.
 narrateur|Le manteau et le gilet, près du four, sentent le pain.</t>
         </is>
       </c>
@@ -17036,17 +17036,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le gilet, le doudou écoute le moineau. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, dans le gilet, écoute le moineau, loin.</t>
+          <t>Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le gilet, le doudou écoute le moineau. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Il écoute le moineau, sans crier. Le doudou, dans le gilet, écoute le moineau, loin.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le gilet, le doudou écoute le moineau. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, dans le gilet, écoute le moineau, loin.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le gilet, le doudou écoute le moineau. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Il écoute le moineau, sans crier. Le doudou, dans le gilet, écoute le moineau, loin.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le pain est sur la table, tout chaud. À toi, on a fini nos phrases. J'ai mis le gilet, le doudou écoute le moineau. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Tu as ouvert, sans tout tirer d'un coup. Le doudou, dans le gilet, écoute le moineau, loin.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus tard, le four s'est tu, et le pain fume. À toi, on a fini nos phrases. J'ai mis le gilet, le doudou écoute le moineau. Sur la table, le pain fume, une miette à part. À table, le moineau chante, trop loin pour le bol. Il écoute le moineau, sans crier. Le doudou, dans le gilet, écoute le moineau, loin.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -17180,12 +17180,12 @@
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, le pain est sur la table, tout chaud.
+          <t>narrateur|Plus tard, le four s'est tu, et le pain fume.
 maman|À toi, on a fini nos phrases.
 enfant-f|J'ai mis le gilet, le doudou écoute le moineau.
 narrateur|Sur la table, le pain fume, une miette à part.
 narrateur|À table, le moineau chante, trop loin pour le bol.
-papa|Tu as ouvert, sans tout tirer d'un coup.
+papa|Il écoute le moineau, sans crier.
 narrateur|Le doudou, dans le gilet, écoute le moineau, loin.</t>
         </is>
       </c>
@@ -17212,7 +17212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17283,6 +17283,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
